--- a/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
   <si>
     <t>VRRM</t>
   </si>
@@ -656,208 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>211000</v>
+      </c>
+      <c r="E8" s="3">
         <v>209900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>204500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>191900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>186100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>197700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>187500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>170400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>170000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>162100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>128700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>89900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>100200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>96900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>79800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>116700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>112500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>128200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>109600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>98500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>370100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>107600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>98200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>69200</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
-      </c>
       <c r="AB8" s="3">
         <v>0</v>
       </c>
@@ -867,83 +870,86 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E9" s="3">
         <v>12000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1000</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>5</v>
       </c>
@@ -953,83 +959,86 @@
       <c r="AD9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>199500</v>
+      </c>
+      <c r="E10" s="3">
         <v>197900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>194200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>182300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>176100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>182200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>175500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>160600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>154000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>151300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>121200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>89000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>94600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>88900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>69700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>106800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>107800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>119600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>105100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>96800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>360900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>104500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>95700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>68200</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1039,8 +1048,11 @@
       <c r="AD10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,8 +1083,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1157,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,29 +1259,32 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1300</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-3000</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
@@ -1279,16 +1298,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>5300</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1300,26 +1319,26 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>5900</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>26500</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>10200</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1329,83 +1348,86 @@
       <c r="AD14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E15" s="3">
         <v>27600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>29100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>30300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>34300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>35000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>34900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>35900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>29500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>27000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>28300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>28800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>29600</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>29200</v>
       </c>
       <c r="R15" s="3">
         <v>29200</v>
       </c>
       <c r="S15" s="3">
+        <v>29200</v>
+      </c>
+      <c r="T15" s="3">
         <v>29300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>28700</v>
-      </c>
-      <c r="U15" s="3">
-        <v>28900</v>
       </c>
       <c r="V15" s="3">
         <v>28900</v>
       </c>
       <c r="W15" s="3">
+        <v>28900</v>
+      </c>
+      <c r="X15" s="3">
         <v>103400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>28800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>27500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>18500</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1415,8 +1437,11 @@
       <c r="AD15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,82 +1469,83 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>187700</v>
+      </c>
+      <c r="E17" s="3">
         <v>152700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>148500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>143200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>144000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>149200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>142300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>138400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>133200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>120200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>97200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>93400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>90100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>81600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>86800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>97300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>88300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>91600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>91900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>80500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>378100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>81400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>86400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>86700</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>200</v>
       </c>
       <c r="AB17" s="3">
         <v>200</v>
@@ -1530,82 +1556,85 @@
       <c r="AD17" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E18" s="3">
         <v>57200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>56000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>48700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>42100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>48500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>45200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>32000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>36800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>41900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>31500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>15300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>19400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>24200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>36600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>18000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>26200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-17500</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-200</v>
       </c>
       <c r="AB18" s="3">
         <v>-200</v>
@@ -1616,8 +1645,11 @@
       <c r="AD18" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,169 +1680,173 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E20" s="3">
         <v>5000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-13600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>13300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>11600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-11200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>18400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-13400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1300</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>1000</v>
       </c>
       <c r="AB20" s="3">
         <v>1000</v>
       </c>
       <c r="AC20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD20" s="3">
         <v>700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E21" s="3">
         <v>89700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>83400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>65400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>88700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>88300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>91300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>66800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>72500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>80000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>51600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>25600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>37700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>49700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>67100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>39900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>68100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>49800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>49100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>24800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>57900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>42000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2400</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1820,83 +1856,86 @@
       <c r="AD21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E22" s="3">
         <v>20400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>22800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>22700</v>
-      </c>
-      <c r="G22" s="3">
-        <v>20300</v>
       </c>
       <c r="H22" s="3">
         <v>20300</v>
       </c>
       <c r="I22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="J22" s="3">
         <v>14500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>9300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>9600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>14100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>14900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>15700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>16000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>69600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>20300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>19600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>12600</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1906,180 +1945,189 @@
       <c r="AD22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E23" s="3">
         <v>41800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>31600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>35000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>33000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>42300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>16900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>28000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>38800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-27700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>25400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>24500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-73200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-28800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E24" s="3">
         <v>11500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-4000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-16300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>500</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD24" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E26" s="3">
         <v>30300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>19100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>28200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>24600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>29600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>27300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-23700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>22100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>17800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-57000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-22200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E27" s="3">
         <v>30300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>19100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>28200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>24600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>29600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>27300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-23700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>22100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>17800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-57000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-22200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2478,8 +2538,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -2496,11 +2556,11 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
@@ -2508,8 +2568,11 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>13600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-13300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-11600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>11200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-18400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>13400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AB32" s="3">
         <v>-1000</v>
       </c>
       <c r="AC32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E33" s="3">
         <v>30300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>28200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>24600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>29600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>27300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-23700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>22100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>17800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-57000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-22200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E35" s="3">
         <v>30300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>28200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>24600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>29600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>27300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-23700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>22100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>17800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-57000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-22200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,94 +3264,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>136300</v>
+      </c>
+      <c r="E41" s="3">
         <v>114400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>210100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>64300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>105200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>51600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>86400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>93400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>101300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>128200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>147300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>249600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>120300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>129200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>113200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>113600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>131500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>135600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>92200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>91500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>65000</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
       <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3351,124 +3440,130 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>244700</v>
+      </c>
+      <c r="E43" s="3">
         <v>237600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>221300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>213900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>199200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>215000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>207700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>214800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>195400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>207200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>244100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>213200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>185200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>157500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>138000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>126400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>114500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>129400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>122300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>111600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>100500</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
+      <c r="Y43" s="3">
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3">
         <v>65000</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
-      </c>
       <c r="AC43" s="3">
         <v>0</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E44" s="3">
         <v>19900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>19800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>19300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>17900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>16500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>15500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12100</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3481,8 +3576,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3523,180 +3618,189 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E45" s="3">
         <v>39300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>91400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>35400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>38900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>32900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>37700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>39400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>39300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>36700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>30100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>20000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>22600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>24900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>19400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>27800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>23200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>20900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>20500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>19600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>17700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>200</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>300</v>
       </c>
       <c r="AD45" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>439500</v>
+      </c>
+      <c r="E46" s="3">
         <v>411300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>542600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>332400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>362600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>317400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>348400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>363000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>348100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>372100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>421600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>482800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>328000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>311600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>270700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>265900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>272400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>288100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>235500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>223600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>185100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>91300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3712,18 +3816,18 @@
       <c r="G47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3">
         <v>3200</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3">
         <v>3700</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3733,8 +3837,8 @@
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3757,204 +3861,213 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y47" s="3">
         <v>406000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>404600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>402900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>402700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>402000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>401100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>156800</v>
+      </c>
+      <c r="E48" s="3">
         <v>153100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>151600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>149400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>147400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>141700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>140900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>139300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>134900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>128700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>129000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>97900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>100100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>103700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>104500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>105400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>208900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>69500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>65900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>71700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>69200</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>65400</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1136900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1148600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1171100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1190000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1210900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1227700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1262600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1298000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1326200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>954800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>982200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>905400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>928600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>946900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>968000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>991700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1018600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1008000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1032900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1057400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1079300</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3">
         <v>498200</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,94 +4241,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E52" s="3">
         <v>43100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>40800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>35400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>28300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>28000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>20500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>27900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>26300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>26500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11100</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>10000</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1790000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1756100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1906200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1710900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1756300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1718300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1779900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1824500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1837100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1481900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1559200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1497200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1367300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1372000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1355100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1374100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1407400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1375900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1346500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1365600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1344800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>406200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>405000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>404800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>664900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>402900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>402400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>401800</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,94 +4576,98 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E57" s="3">
         <v>89800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>78400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>71500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>79900</v>
-      </c>
-      <c r="H57" s="3">
-        <v>69100</v>
       </c>
       <c r="I57" s="3">
         <v>69100</v>
       </c>
       <c r="J57" s="3">
+        <v>69100</v>
+      </c>
+      <c r="K57" s="3">
         <v>63000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>67600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>48600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>47400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>41300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>34500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>45600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>36300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>39200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>50800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>57200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>49300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>52200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>45200</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>20200</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4548,31 +4681,31 @@
         <v>9000</v>
       </c>
       <c r="G58" s="3">
+        <v>9000</v>
+      </c>
+      <c r="H58" s="3">
         <v>21900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>12000</v>
       </c>
       <c r="J58" s="3">
         <v>12000</v>
       </c>
       <c r="K58" s="3">
+        <v>12000</v>
+      </c>
+      <c r="L58" s="3">
         <v>37000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>9400</v>
       </c>
       <c r="M58" s="3">
         <v>9400</v>
       </c>
       <c r="N58" s="3">
+        <v>9400</v>
+      </c>
+      <c r="O58" s="3">
         <v>6500</v>
-      </c>
-      <c r="O58" s="3">
-        <v>9100</v>
       </c>
       <c r="P58" s="3">
         <v>9100</v>
@@ -4584,10 +4717,10 @@
         <v>9100</v>
       </c>
       <c r="S58" s="3">
+        <v>9100</v>
+      </c>
+      <c r="T58" s="3">
         <v>28800</v>
-      </c>
-      <c r="T58" s="3">
-        <v>9100</v>
       </c>
       <c r="U58" s="3">
         <v>9100</v>
@@ -4598,8 +4731,8 @@
       <c r="W58" s="3">
         <v>9100</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
+      <c r="X58" s="3">
+        <v>9100</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>5</v>
@@ -4607,258 +4740,267 @@
       <c r="Z58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>3300</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
       <c r="AC58" s="3">
         <v>0</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E59" s="3">
         <v>98800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>93400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>88100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>85000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>82900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>84400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>79100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>70700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>58900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>49900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>22600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>23700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>36100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>24000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>20300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>30400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>100</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>400</v>
       </c>
       <c r="AD59" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>214800</v>
+      </c>
+      <c r="E60" s="3">
         <v>197600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>180800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>168600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>186800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>161100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>165500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>154100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>175200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>116900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>106700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>70400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>64000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>72000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>65000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>72000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>104900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>90300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>78700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>91800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>68700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>33500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>100</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>400</v>
       </c>
       <c r="AD60" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1029100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1030400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1129700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1140700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1190000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1204000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1205200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1206300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1206800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>965400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>966100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>965900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>832900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>833600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>834300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>835500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>837700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>858200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>859100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>859800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>860200</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4866,84 +5008,87 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>425400</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>124600</v>
+      </c>
+      <c r="E62" s="3">
         <v>124100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>130400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>164400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>148300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>158300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>165000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>188200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>195100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>156000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>170000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>152300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>154800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>122400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>124000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>122200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>155200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>99800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>98800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>109200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>113700</v>
-      </c>
-      <c r="X62" s="3">
-        <v>14000</v>
       </c>
       <c r="Y62" s="3">
         <v>14000</v>
@@ -4952,19 +5097,22 @@
         <v>14000</v>
       </c>
       <c r="AA62" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AB62" s="3">
         <v>73500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>14500</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>14000</v>
       </c>
       <c r="AD62" s="3">
         <v>14000</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,94 +5375,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1368500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1352000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1440900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1473800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1525200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1523400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1535600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1548700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1577100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1238300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1242800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1188700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1051800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1028000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1023400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1029700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1097800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1048300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1036600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1060800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1042700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>18900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>517600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14700</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>14400</v>
       </c>
       <c r="AD66" s="3">
         <v>14400</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-125900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-128900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-74400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-93500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-98100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-128200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-90900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-71400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-81400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-100500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-99800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-103800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-94900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-82900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-89600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-74200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-89600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-89400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-107200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-110700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-113300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>421500</v>
+      </c>
+      <c r="E76" s="3">
         <v>404100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>465300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>237100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>231100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>194900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>244200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>275800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>260000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>243700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>316400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>308500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>315600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>343900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>331800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>344400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>309600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>327600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>309800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>304800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>302100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>387200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>387900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>389500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>147300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>388200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>388000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>387400</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E81" s="3">
         <v>30300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>28200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>24600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>29600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>27300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-23700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>22100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>17800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-57000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-22200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,83 +6605,84 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E83" s="3">
         <v>27500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>29000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>33400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>35100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>34500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>35700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>32000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>29500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>27000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>28200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>28700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>29400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>29200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>29300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>29100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>28700</v>
-      </c>
-      <c r="U83" s="3">
-        <v>28900</v>
       </c>
       <c r="V83" s="3">
         <v>28900</v>
       </c>
       <c r="W83" s="3">
+        <v>28900</v>
+      </c>
+      <c r="X83" s="3">
         <v>28500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>28800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>27500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>18600</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
-      </c>
       <c r="AB83" s="3">
         <v>0</v>
       </c>
@@ -6494,8 +6692,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E89" s="3">
         <v>62400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>62700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>45200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>69600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>52400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>65100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>31200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>63900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>91800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>28500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>14800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>38200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>49800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>37400</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>33500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>11500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,83 +7261,84 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-9200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
@@ -7128,8 +7348,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,94 +7526,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-353600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-111500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-37500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-559600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-400300</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7504,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,166 +8004,172 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-146400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>94500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-66600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-73000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-57900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-28700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>263400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-101700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-16900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>123900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6100</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-2400</v>
       </c>
       <c r="Q100" s="3">
         <v>-2400</v>
       </c>
       <c r="R100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="S100" s="3">
         <v>-23100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-7400</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-2400</v>
       </c>
       <c r="U100" s="3">
         <v>-2400</v>
       </c>
       <c r="V100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="W100" s="3">
         <v>-2300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>31600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>548000</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>401500</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-500</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
@@ -7934,90 +8182,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-95200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>145700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-41300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>53500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-34900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-26800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-19300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-99900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>129500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>43700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>26100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>22000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>13800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>7400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>VRRM</t>
   </si>
@@ -656,214 +656,218 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>209700</v>
+      </c>
+      <c r="E8" s="3">
         <v>211000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>209900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>204500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>191900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>186100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>197700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>187500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>170400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>170000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>162100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>128700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>89900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>100200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>96900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>79800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>116700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>112500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>128200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>109600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>98500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>370100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>107600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>98200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>69200</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
-      </c>
       <c r="AC8" s="3">
         <v>0</v>
       </c>
@@ -873,86 +877,89 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E9" s="3">
         <v>11500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1000</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
@@ -962,86 +969,89 @@
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>200100</v>
+      </c>
+      <c r="E10" s="3">
         <v>199500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>197900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>194200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>182300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>176100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>182200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>175500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>160600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>154000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>151300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>121200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>89000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>94600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>88900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>69700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>106800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>107800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>119600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>105100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>96800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>360900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>104500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>95700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>68200</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1051,8 +1061,11 @@
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,32 +1279,35 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>2000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1300</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-3000</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
@@ -1301,16 +1321,16 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>5300</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1322,26 +1342,26 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>5900</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>26500</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>10200</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1351,86 +1371,89 @@
       <c r="AE14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E15" s="3">
         <v>26200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>27600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>29100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>30300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>34300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>35000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>34900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>35900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>29500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>27000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>28300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>28800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>29600</v>
-      </c>
-      <c r="R15" s="3">
-        <v>29200</v>
       </c>
       <c r="S15" s="3">
         <v>29200</v>
       </c>
       <c r="T15" s="3">
+        <v>29200</v>
+      </c>
+      <c r="U15" s="3">
         <v>29300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>28700</v>
-      </c>
-      <c r="V15" s="3">
-        <v>28900</v>
       </c>
       <c r="W15" s="3">
         <v>28900</v>
       </c>
       <c r="X15" s="3">
+        <v>28900</v>
+      </c>
+      <c r="Y15" s="3">
         <v>103400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>28800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>27500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>18500</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,85 +1496,86 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E17" s="3">
         <v>187700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>152700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>148500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>143200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>144000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>149200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>142300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>138400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>133200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>120200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>97200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>93400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>90100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>81600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>86800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>97300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>88300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>91600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>91900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>80500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>378100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>81400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>86400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>86700</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>200</v>
       </c>
       <c r="AC17" s="3">
         <v>200</v>
@@ -1559,85 +1586,88 @@
       <c r="AE17" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E18" s="3">
         <v>23300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>57200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>56000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>48700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>42100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>48500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>45200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>32000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>36800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>41900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>31500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>15300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>19400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>24200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>36600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>18000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>26200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-17500</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-200</v>
       </c>
       <c r="AC18" s="3">
         <v>-200</v>
@@ -1648,8 +1678,11 @@
       <c r="AE18" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,175 +1714,179 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-13600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>13300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>11600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-11200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>18400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-13400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1300</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>1000</v>
       </c>
       <c r="AC20" s="3">
         <v>1000</v>
       </c>
       <c r="AD20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE20" s="3">
         <v>700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>85500</v>
+      </c>
+      <c r="E21" s="3">
         <v>48200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>89700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>83400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>65400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>88700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>88300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>91300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>66800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>72500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>80000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>51600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>25600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>37700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>49700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>67100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>39900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>68100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>49800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>49100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>24800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>57900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>42000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2400</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1859,86 +1896,89 @@
       <c r="AE21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E22" s="3">
         <v>20900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>20400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>22800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>20300</v>
       </c>
       <c r="I22" s="3">
         <v>20300</v>
       </c>
       <c r="J22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="K22" s="3">
         <v>14500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>9200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>9300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>14100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>14900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>15700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>16000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>69600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>20300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>19600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>12600</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1948,186 +1988,195 @@
       <c r="AE22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>41800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>31600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>35000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>33000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>42300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>16900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>28000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>38800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-27700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>25400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>24500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-73200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-28800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-4000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-16300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>500</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE24" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E26" s="3">
         <v>3000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>30300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>19100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>28200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>24600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>29600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>27300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-23700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>22100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>17800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-57000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-22200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E27" s="3">
         <v>3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>30300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>19100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>28200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>24600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>29600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>27300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-23700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>22100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>17800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-57000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-22200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2541,8 +2602,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
@@ -2559,11 +2620,11 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2816,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E32" s="3">
         <v>1300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>13600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-13300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-11600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>11200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-18400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>13400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AC32" s="3">
         <v>-1000</v>
       </c>
       <c r="AD32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E33" s="3">
         <v>3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>30300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>19100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>28200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>24600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>29600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>27300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-23700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>22100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>17800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-57000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-22200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E35" s="3">
         <v>3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>30300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>19100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>28200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>24600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>29600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>27300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-23700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>22100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>17800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-57000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-22200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3351,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>149500</v>
+      </c>
+      <c r="E41" s="3">
         <v>136300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>114400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>210100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>64300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>105200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>51600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>86400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>93400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>101300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>128200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>147300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>249600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>120300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>129200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>113200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>113600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>131500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>135600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>92200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>91500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>65000</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
       <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
         <v>200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,130 +3533,136 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>230100</v>
+      </c>
+      <c r="E43" s="3">
         <v>244700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>237600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>221300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>213900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>199200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>215000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>207700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>214800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>195400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>207200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>244100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>213200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>185200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>157500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>138000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>126400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>114500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>129400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>122300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>111600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>100500</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
+      <c r="Z43" s="3">
+        <v>0</v>
       </c>
       <c r="AA43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3">
         <v>65000</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
       <c r="AD43" s="3">
         <v>0</v>
       </c>
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E44" s="3">
         <v>18000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>19900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>19800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>18900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>19300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>17900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>16500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>15500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12100</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3579,8 +3675,8 @@
       <c r="Q44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -3621,186 +3717,195 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E45" s="3">
         <v>40500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>39300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>91400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>35400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>38900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>37700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>39400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>39300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>36700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>30100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>20000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>22600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>24900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>19400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>26000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>27800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>23200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>20900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>20500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>19600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>17700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>200</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>300</v>
       </c>
       <c r="AE45" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>438600</v>
+      </c>
+      <c r="E46" s="3">
         <v>439500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>411300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>542600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>332400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>362600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>317400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>348400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>363000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>348100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>372100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>421600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>482800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>328000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>311600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>270700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>265900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>272400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>288100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>235500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>223600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>185100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>91300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3819,18 +3924,18 @@
       <c r="H47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3">
         <v>3200</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
         <v>3700</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3840,8 +3945,8 @@
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3864,210 +3969,219 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y47" s="3">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
         <v>406000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>404600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>402900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>402700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>402000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>401100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>158600</v>
+      </c>
+      <c r="E48" s="3">
         <v>156800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>153100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>151600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>149400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>147400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>141700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>140900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>139300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>134900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>128700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>129000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>97900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>100100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>103700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>104500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>105400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>208900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>69500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>65900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>71700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>69200</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>65400</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1118000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1136900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1148600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1171100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1190000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1210900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1227700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1262600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1298000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1326200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>954800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>982200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>905400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>928600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>946900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>968000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>991700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1018600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1008000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1032900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1057400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1079300</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3">
         <v>498200</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4361,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E52" s="3">
         <v>56800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>43100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>40800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>39100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>35400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>28300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>28000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>20500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>27900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>26300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>26500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>12000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11100</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>10000</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1769900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1790000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1756100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1906200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1710900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1756300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1718300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1779900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1824500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1837100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1481900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1559200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1497200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1367300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1372000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1355100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1374100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1407400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1375900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1346500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1365600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1344800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>406200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>405000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>404800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>664900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>402900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>402400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>401800</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,102 +4707,106 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>75600</v>
+      </c>
+      <c r="E57" s="3">
         <v>78700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>89800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>78400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>71500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>79900</v>
-      </c>
-      <c r="I57" s="3">
-        <v>69100</v>
       </c>
       <c r="J57" s="3">
         <v>69100</v>
       </c>
       <c r="K57" s="3">
+        <v>69100</v>
+      </c>
+      <c r="L57" s="3">
         <v>63000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>67600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>48600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>47400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>41300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>34500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>45600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>36300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>39200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>50800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>57200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>49300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>52200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>45200</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3">
         <v>20200</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>9000</v>
@@ -4684,31 +4818,31 @@
         <v>9000</v>
       </c>
       <c r="H58" s="3">
+        <v>9000</v>
+      </c>
+      <c r="I58" s="3">
         <v>21900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>12000</v>
       </c>
       <c r="K58" s="3">
         <v>12000</v>
       </c>
       <c r="L58" s="3">
+        <v>12000</v>
+      </c>
+      <c r="M58" s="3">
         <v>37000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>9400</v>
       </c>
       <c r="N58" s="3">
         <v>9400</v>
       </c>
       <c r="O58" s="3">
+        <v>9400</v>
+      </c>
+      <c r="P58" s="3">
         <v>6500</v>
-      </c>
-      <c r="P58" s="3">
-        <v>9100</v>
       </c>
       <c r="Q58" s="3">
         <v>9100</v>
@@ -4720,10 +4854,10 @@
         <v>9100</v>
       </c>
       <c r="T58" s="3">
+        <v>9100</v>
+      </c>
+      <c r="U58" s="3">
         <v>28800</v>
-      </c>
-      <c r="U58" s="3">
-        <v>9100</v>
       </c>
       <c r="V58" s="3">
         <v>9100</v>
@@ -4734,8 +4868,8 @@
       <c r="X58" s="3">
         <v>9100</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
+      <c r="Y58" s="3">
+        <v>9100</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>5</v>
@@ -4743,267 +4877,276 @@
       <c r="AA58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3">
         <v>3300</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
       <c r="AD58" s="3">
         <v>0</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E59" s="3">
         <v>127000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>98800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>93400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>88100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>85000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>82900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>84400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>79100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>70700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>58900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>49900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>22600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>23700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>36100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>24000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>20300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>30400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>100</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>400</v>
       </c>
       <c r="AE59" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>159400</v>
+      </c>
+      <c r="E60" s="3">
         <v>214800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>197600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>180800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>168600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>186800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>161100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>165500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>154100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>175200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>116900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>106700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>70400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>64000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>72000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>65000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>72000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>104900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>90300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>78700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>91800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>68700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>33500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>100</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>400</v>
       </c>
       <c r="AE60" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1037700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1029100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1030400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1129700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1140700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1190000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1204000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1205200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1206300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1206800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>965400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>966100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>965900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>832900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>833600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>834300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>835500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>837700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>858200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>859100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>859800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>860200</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5011,87 +5154,90 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>425400</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>123700</v>
+      </c>
+      <c r="E62" s="3">
         <v>124600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>124100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>130400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>164400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>148300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>158300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>165000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>188200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>195100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>156000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>170000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>152300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>154800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>122400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>124000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>122200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>155200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>99800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>98800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>109200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>113700</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>14000</v>
       </c>
       <c r="Z62" s="3">
         <v>14000</v>
@@ -5100,19 +5246,22 @@
         <v>14000</v>
       </c>
       <c r="AB62" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AC62" s="3">
         <v>73500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>14500</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>14000</v>
       </c>
       <c r="AE62" s="3">
         <v>14000</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1320900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1368500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1352000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1440900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1473800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1525200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1523400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1535600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1548700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1577100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1238300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1242800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1188700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1051800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1028000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1023400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1029700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1097800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1048300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1036600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1060800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1042700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>18900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>517600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14700</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>14400</v>
       </c>
       <c r="AE66" s="3">
         <v>14400</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-94900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-125900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-128900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-74400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-93500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-98100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-128200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-90900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-71400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-81400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-100500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-99800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-103800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-94900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-82900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-89600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-74200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-89600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-89400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-107200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-110700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-113300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>449000</v>
+      </c>
+      <c r="E76" s="3">
         <v>421500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>404100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>465300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>237100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>231100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>194900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>244200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>275800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>260000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>243700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>316400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>308500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>315600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>343900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>331800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>344400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>309600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>327600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>309800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>304800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>302100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>387200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>387900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>389500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>147300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>388200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>388000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>387400</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E81" s="3">
         <v>3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>30300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>19100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>28200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>24600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>29600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>27300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-23700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>22100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>17800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-57000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-22200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,86 +6804,87 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E83" s="3">
         <v>26200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>27500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>29000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>30300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>33400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>35100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>35700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>32000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>29500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>27000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>28200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>28700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>29400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>29200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>29300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>29100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>28700</v>
-      </c>
-      <c r="V83" s="3">
-        <v>28900</v>
       </c>
       <c r="W83" s="3">
         <v>28900</v>
       </c>
       <c r="X83" s="3">
+        <v>28900</v>
+      </c>
+      <c r="Y83" s="3">
         <v>28500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>28800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>27500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>18600</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
-      </c>
       <c r="AC83" s="3">
         <v>0</v>
       </c>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E89" s="3">
         <v>35700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>62400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>62700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>45200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>69600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>52400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>65100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>31200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>63900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>91800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>28500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>21800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>7700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>14800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>38200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>49800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>37400</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>33500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>11500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,86 +7482,87 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-12200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-9200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-16600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-353600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-111500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-37500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-9200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-559600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-400300</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,172 +8250,178 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-146400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>94500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-66600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-73000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-57900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-28700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>263400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-101700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-16900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>123900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6100</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-2400</v>
       </c>
       <c r="R100" s="3">
         <v>-2400</v>
       </c>
       <c r="S100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="T100" s="3">
         <v>-23100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-7400</v>
-      </c>
-      <c r="U100" s="3">
-        <v>-2400</v>
       </c>
       <c r="V100" s="3">
         <v>-2400</v>
       </c>
       <c r="W100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="X100" s="3">
         <v>-2300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>31600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>548000</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>401500</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
         <v>1600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-500</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
@@ -8185,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E102" s="3">
         <v>21400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-95200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>145700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-41300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>53500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-34900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-26800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-99900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>129500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-17300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>43700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>26100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>13400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>22000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>13800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>7400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>VRRM</t>
   </si>
@@ -656,221 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>222400</v>
+      </c>
+      <c r="E8" s="3">
         <v>209700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>211000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>209900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>204500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>191900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>186100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>197700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>187500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>170400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>170000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>162100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>128700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>89900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>100200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>96900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>79800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>116700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>112500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>128200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>109600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>98500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>370100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>107600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>98200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>69200</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
-      </c>
       <c r="AD8" s="3">
         <v>0</v>
       </c>
@@ -880,89 +884,92 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E9" s="3">
         <v>9600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1000</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>5</v>
       </c>
@@ -972,89 +979,92 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>209900</v>
+      </c>
+      <c r="E10" s="3">
         <v>200100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>199500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>197900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>194200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>182300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>176100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>182200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>175500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>160600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>154000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>151300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>121200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>89000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>94600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>88900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>69700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>106800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>107800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>119600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>105100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>96800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>360900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>104500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>95700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>68200</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1064,8 +1074,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,35 +1299,38 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>600</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>2000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1300</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-3000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1324,16 +1344,16 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>5300</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1345,26 +1365,26 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>5900</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>26500</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>10200</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1374,89 +1394,92 @@
       <c r="AF14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E15" s="3">
         <v>27000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>26200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>27600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>29100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>30300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>34300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>35000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>34900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>35900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>32000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>29500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>27000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>28300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>28800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>29600</v>
-      </c>
-      <c r="S15" s="3">
-        <v>29200</v>
       </c>
       <c r="T15" s="3">
         <v>29200</v>
       </c>
       <c r="U15" s="3">
+        <v>29200</v>
+      </c>
+      <c r="V15" s="3">
         <v>29300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>28700</v>
-      </c>
-      <c r="W15" s="3">
-        <v>28900</v>
       </c>
       <c r="X15" s="3">
         <v>28900</v>
       </c>
       <c r="Y15" s="3">
+        <v>28900</v>
+      </c>
+      <c r="Z15" s="3">
         <v>103400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>28800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>27500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>18500</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,88 +1523,89 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>161300</v>
+      </c>
+      <c r="E17" s="3">
         <v>156000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>187700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>152700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>148500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>143200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>144000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>149200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>142300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>138400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>133200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>120200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>97200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>93400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>90100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>81600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>86800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>97300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>88300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>91600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>91900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>80500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>378100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>81400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>86400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>86700</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>200</v>
       </c>
       <c r="AD17" s="3">
         <v>200</v>
@@ -1589,88 +1616,91 @@
       <c r="AF17" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>61100</v>
+      </c>
+      <c r="E18" s="3">
         <v>53700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>23300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>57200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>56000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>48700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>42100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>48500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>45200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>32000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>36800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>41900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>31500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>19400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>24200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>36600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>17700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>18000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>26200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-17500</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-200</v>
       </c>
       <c r="AD18" s="3">
         <v>-200</v>
@@ -1681,8 +1711,11 @@
       <c r="AF18" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,181 +1748,185 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E20" s="3">
         <v>4900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-13600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>13300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-11200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>18400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-13400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>4400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1300</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>1000</v>
       </c>
       <c r="AD20" s="3">
         <v>1000</v>
       </c>
       <c r="AE20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF20" s="3">
         <v>700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>93900</v>
+      </c>
+      <c r="E21" s="3">
         <v>85500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>48200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>89700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>83400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>65400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>88700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>88300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>91300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>66800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>72500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>80000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>51600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>25600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>37700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>49700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>67100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>39900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>68100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>49800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>49100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>24800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>57900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>42000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2400</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1899,89 +1936,92 @@
       <c r="AF21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E22" s="3">
         <v>19600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>20900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>20400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22700</v>
-      </c>
-      <c r="I22" s="3">
-        <v>20300</v>
       </c>
       <c r="J22" s="3">
         <v>20300</v>
       </c>
       <c r="K22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="L22" s="3">
         <v>14500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>9200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>9500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>14100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>14900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>15700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>16000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>69600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>19600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>12600</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1991,192 +2031,201 @@
       <c r="AF22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E23" s="3">
         <v>39000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>41800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>31600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>35000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>33000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>42300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>16900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>28000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>38800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>10700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-27700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>25400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>24500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-73200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-28800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E24" s="3">
         <v>9800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-4000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-16300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>500</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF24" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E26" s="3">
         <v>29100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>30300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>19100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>28200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>24600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>29600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>27300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-23700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>22100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>17800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-57000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-22200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E27" s="3">
         <v>29100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>30300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>19100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>28200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>24600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>29600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>27300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-23700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>22100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>17800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-57000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-22200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2605,8 +2666,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
@@ -2623,11 +2684,11 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>13600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-13300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>11200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-18400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>13400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AD32" s="3">
         <v>-1000</v>
       </c>
       <c r="AE32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E33" s="3">
         <v>29100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>30300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>19100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>28200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>24600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>29600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>27300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-23700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>22100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>17800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-57000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-22200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E35" s="3">
         <v>29100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>30300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>19100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>28200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>24600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>29600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>27300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-23700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>22100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>17800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-57000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-22200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3438,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E41" s="3">
         <v>149500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>136300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>114400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>210100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>64300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>105200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>51600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>86400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>93400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>101300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>128200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>147300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>249600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>120300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>129200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>113200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>113600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>131500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>135600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>92200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>91500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>65000</v>
       </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
       <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="3">
         <v>200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,136 +3626,142 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>268200</v>
+      </c>
+      <c r="E43" s="3">
         <v>230100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>244700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>237600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>221300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>213900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>199200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>215000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>207700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>214800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>195400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>207200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>244100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>213200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>185200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>157500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>138000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>126400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>114500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>129400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>122300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>111600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>100500</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="3" t="s">
-        <v>5</v>
+      <c r="AA43" s="3">
+        <v>0</v>
       </c>
       <c r="AB43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
         <v>65000</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
       <c r="AE43" s="3">
         <v>0</v>
       </c>
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E44" s="3">
         <v>17300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>18000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>19900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>19800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>18900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>19300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>17900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>16500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>15500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12100</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3678,8 +3774,8 @@
       <c r="R44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -3720,192 +3816,201 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E45" s="3">
         <v>41600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>40500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>39300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>91400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>38900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>32900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>37700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>39400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>39300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>36700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>30100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>20000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>22600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>24900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>19400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>26000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>27800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>23200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>20900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>20500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>19600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>17700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>200</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>300</v>
       </c>
       <c r="AF45" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>449600</v>
+      </c>
+      <c r="E46" s="3">
         <v>438600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>439500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>411300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>542600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>332400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>362600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>317400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>348400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>363000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>348100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>372100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>421600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>482800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>328000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>311600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>270700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>265900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>272400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>288100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>235500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>223600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>185100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>91300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3927,18 +4032,18 @@
       <c r="I47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3">
         <v>3200</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3">
         <v>3700</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3948,8 +4053,8 @@
       <c r="P47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3972,216 +4077,225 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="3">
         <v>406000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>404600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>402900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>402700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>402000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>401100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>163700</v>
+      </c>
+      <c r="E48" s="3">
         <v>158600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>156800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>153100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>151600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>149400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>147400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>141700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>140900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>139300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>134900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>128700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>129000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>97900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>100100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>103700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>104500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>105400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>208900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>69500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>65900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>71700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>69200</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>65400</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1101700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1118000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1136900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1148600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1171100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1190000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1210900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1227700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1262600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1298000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1326200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>954800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>982200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>905400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>928600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>946900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>968000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>991700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1018600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1008000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1032900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1057400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1079300</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD49" s="3">
         <v>498200</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4481,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E52" s="3">
         <v>54700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>56800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>43100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>40800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>39100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>35400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>28300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>20500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>27900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>26300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>26500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11100</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>10000</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1773000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1769900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1790000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1756100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1906200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1710900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1756300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1718300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1779900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1824500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1837100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1481900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1559200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1497200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1367300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1372000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1355100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1374100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1407400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1375900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1346500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1365600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1344800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>406200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>405000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>404800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>664900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>402900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>402400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>401800</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,100 +4838,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>84900</v>
+      </c>
+      <c r="E57" s="3">
         <v>75600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>78700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>89800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>78400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>71500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>79900</v>
-      </c>
-      <c r="J57" s="3">
-        <v>69100</v>
       </c>
       <c r="K57" s="3">
         <v>69100</v>
       </c>
       <c r="L57" s="3">
+        <v>69100</v>
+      </c>
+      <c r="M57" s="3">
         <v>63000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>67600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>48600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>47400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>41300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>34500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>45600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>36300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>39200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>50800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>57200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>49300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>52200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>45200</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>20200</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4809,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>9000</v>
@@ -4821,31 +4955,31 @@
         <v>9000</v>
       </c>
       <c r="I58" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J58" s="3">
         <v>21900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>12000</v>
       </c>
       <c r="L58" s="3">
         <v>12000</v>
       </c>
       <c r="M58" s="3">
+        <v>12000</v>
+      </c>
+      <c r="N58" s="3">
         <v>37000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>9400</v>
       </c>
       <c r="O58" s="3">
         <v>9400</v>
       </c>
       <c r="P58" s="3">
+        <v>9400</v>
+      </c>
+      <c r="Q58" s="3">
         <v>6500</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>9100</v>
       </c>
       <c r="R58" s="3">
         <v>9100</v>
@@ -4857,10 +4991,10 @@
         <v>9100</v>
       </c>
       <c r="U58" s="3">
+        <v>9100</v>
+      </c>
+      <c r="V58" s="3">
         <v>28800</v>
-      </c>
-      <c r="V58" s="3">
-        <v>9100</v>
       </c>
       <c r="W58" s="3">
         <v>9100</v>
@@ -4871,8 +5005,8 @@
       <c r="Y58" s="3">
         <v>9100</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
+      <c r="Z58" s="3">
+        <v>9100</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>5</v>
@@ -4880,276 +5014,285 @@
       <c r="AB58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>3300</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
-      </c>
       <c r="AE58" s="3">
         <v>0</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>90400</v>
+      </c>
+      <c r="E59" s="3">
         <v>83900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>127000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>98800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>93400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>88100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>85000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>82900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>84400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>79100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>70700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>58900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>49900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>20400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>19600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>23700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>36100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>24000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>20300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>30400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>100</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>400</v>
       </c>
       <c r="AF59" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>175300</v>
+      </c>
+      <c r="E60" s="3">
         <v>159400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>214800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>197600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>180800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>168600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>186800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>161100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>165500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>154100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>175200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>116900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>106700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>70400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>64000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>72000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>65000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>72000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>104900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>90300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>78700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>91800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>68700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>33500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>100</v>
-      </c>
-      <c r="AE60" s="3">
-        <v>400</v>
       </c>
       <c r="AF60" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1036300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1037700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1029100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1030400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1129700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1140700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1190000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1204000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1205200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1206300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1206800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>965400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>966100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>965900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>832900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>833600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>834300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>835500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>837700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>858200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>859100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>859800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>860200</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5157,90 +5300,93 @@
         <v>0</v>
       </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>425400</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>122700</v>
+      </c>
+      <c r="E62" s="3">
         <v>123700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>124600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>124100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>130400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>164400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>148300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>158300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>165000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>188200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>195100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>156000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>170000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>152300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>154800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>122400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>124000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>122200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>155200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>99800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>98800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>109200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>113700</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>14000</v>
       </c>
       <c r="AA62" s="3">
         <v>14000</v>
@@ -5249,19 +5395,22 @@
         <v>14000</v>
       </c>
       <c r="AC62" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AD62" s="3">
         <v>73500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>14500</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>14000</v>
       </c>
       <c r="AF62" s="3">
         <v>14000</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1334400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1320900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1368500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1352000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1440900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1473800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1525200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1523400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1535600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1548700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1577100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1238300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1242800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1188700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1051800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1028000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1023400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1029700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1097800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1048300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1036600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1060800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1042700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>18900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>17100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>517600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14700</v>
-      </c>
-      <c r="AE66" s="3">
-        <v>14400</v>
       </c>
       <c r="AF66" s="3">
         <v>14400</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-105900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-94900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-125900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-128900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-74400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-93500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-98100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-128200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-90900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-71400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-81400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-100500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-99800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-103800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-94900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-82900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-89600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-74200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-89600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-89400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-107200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-110700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-113300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>18200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>438600</v>
+      </c>
+      <c r="E76" s="3">
         <v>449000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>421500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>404100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>465300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>237100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>231100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>194900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>244200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>275800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>260000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>243700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>316400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>308500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>315600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>343900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>331800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>344400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>309600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>327600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>309800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>304800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>302100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>387200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>387900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>389500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>147300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>388200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>388000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>387400</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E81" s="3">
         <v>29100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>30300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>19100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>28200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>24600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>29600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>27300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-23700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>22100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>17800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-57000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-22200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,89 +7003,90 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E83" s="3">
         <v>26900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>26200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>27500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>29000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>30300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>33400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>35100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>34500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>35700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>32000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>29500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>27000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>28200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>28700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>29400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>29200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>29300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>29100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>28700</v>
-      </c>
-      <c r="W83" s="3">
-        <v>28900</v>
       </c>
       <c r="X83" s="3">
         <v>28900</v>
       </c>
       <c r="Y83" s="3">
+        <v>28900</v>
+      </c>
+      <c r="Z83" s="3">
         <v>28500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>28800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>27500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>18600</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
-      </c>
       <c r="AD83" s="3">
         <v>0</v>
       </c>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E89" s="3">
         <v>34300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>35700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>62400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>62700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>45200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>69600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>52400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>65100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>31200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>63900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>91800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>28500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>21800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>7700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>14800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>38200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>49800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>37400</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>33500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>11500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,89 +7703,90 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-12200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-16600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-353600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-111500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-37500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-559600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-400300</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,178 +8496,184 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-146400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>94500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-66600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-73000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-57900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-28700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>263400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-101700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-16900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>123900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6100</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-2400</v>
       </c>
       <c r="S100" s="3">
         <v>-2400</v>
       </c>
       <c r="T100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="U100" s="3">
         <v>-23100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-7400</v>
-      </c>
-      <c r="V100" s="3">
-        <v>-2400</v>
       </c>
       <c r="W100" s="3">
         <v>-2400</v>
       </c>
       <c r="X100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>31600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>548000</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>401500</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-500</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
@@ -8437,96 +8686,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E102" s="3">
         <v>13500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>21400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-95200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>145700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-41300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>53500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-34900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-26800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-99900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>129500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-17300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-5300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>43700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>26100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>13400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>22000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>7400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>VRRM</t>
   </si>
@@ -656,228 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>225600</v>
+      </c>
+      <c r="E8" s="3">
         <v>222400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>209700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>211000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>209900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>204500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>191900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>186100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>197700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>187500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>170400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>170000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>162100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>128700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>89900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>100200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>96900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>79800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>116700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>112500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>128200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>109600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>98500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>370100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>107600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>98200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>69200</v>
       </c>
-      <c r="AD8" s="3">
-        <v>0</v>
-      </c>
       <c r="AE8" s="3">
         <v>0</v>
       </c>
@@ -887,92 +891,95 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>12500</v>
+        <v>87000</v>
       </c>
       <c r="E9" s="3">
-        <v>9600</v>
+        <v>87400</v>
       </c>
       <c r="F9" s="3">
-        <v>11500</v>
+        <v>80200</v>
       </c>
       <c r="G9" s="3">
+        <v>84600</v>
+      </c>
+      <c r="H9" s="3">
+        <v>80900</v>
+      </c>
+      <c r="I9" s="3">
+        <v>76000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>71500</v>
+      </c>
+      <c r="K9" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L9" s="3">
+        <v>15500</v>
+      </c>
+      <c r="M9" s="3">
         <v>12000</v>
       </c>
-      <c r="H9" s="3">
-        <v>10300</v>
-      </c>
-      <c r="I9" s="3">
-        <v>9600</v>
-      </c>
-      <c r="J9" s="3">
-        <v>10000</v>
-      </c>
-      <c r="K9" s="3">
-        <v>15500</v>
-      </c>
-      <c r="L9" s="3">
-        <v>12000</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1000</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
@@ -982,92 +989,95 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>209900</v>
+        <v>138500</v>
       </c>
       <c r="E10" s="3">
-        <v>200100</v>
+        <v>135000</v>
       </c>
       <c r="F10" s="3">
-        <v>199500</v>
+        <v>129500</v>
       </c>
       <c r="G10" s="3">
-        <v>197900</v>
+        <v>126500</v>
       </c>
       <c r="H10" s="3">
-        <v>194200</v>
+        <v>129000</v>
       </c>
       <c r="I10" s="3">
-        <v>182300</v>
+        <v>128500</v>
       </c>
       <c r="J10" s="3">
+        <v>120400</v>
+      </c>
+      <c r="K10" s="3">
         <v>176100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>182200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>175500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>160600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>154000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>151300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>121200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>89000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>94600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>88900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>69700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>106800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>107800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>119600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>105100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>96800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>360900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>104500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>95700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>68200</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1077,8 +1087,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1125,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1221,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,38 +1319,41 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>35800</v>
+      </c>
+      <c r="H14" s="3">
         <v>2000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1300</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-3000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1347,16 +1367,16 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>5300</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1368,26 +1388,26 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>5900</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>26500</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>10200</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1397,92 +1417,95 @@
       <c r="AG14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E15" s="3">
         <v>27500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>27000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>26200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>27600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>29100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>30300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>34300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>35000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>34900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>35900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>32000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>29500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>27000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>28300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>28800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>29600</v>
-      </c>
-      <c r="T15" s="3">
-        <v>29200</v>
       </c>
       <c r="U15" s="3">
         <v>29200</v>
       </c>
       <c r="V15" s="3">
+        <v>29200</v>
+      </c>
+      <c r="W15" s="3">
         <v>29300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>28700</v>
-      </c>
-      <c r="X15" s="3">
-        <v>28900</v>
       </c>
       <c r="Y15" s="3">
         <v>28900</v>
       </c>
       <c r="Z15" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AA15" s="3">
         <v>103400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>28800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>27500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>18500</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,91 +1550,92 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>161700</v>
+      </c>
+      <c r="E17" s="3">
         <v>161300</v>
       </c>
-      <c r="E17" s="3">
-        <v>156000</v>
-      </c>
       <c r="F17" s="3">
-        <v>187700</v>
+        <v>155400</v>
       </c>
       <c r="G17" s="3">
-        <v>152700</v>
+        <v>151900</v>
       </c>
       <c r="H17" s="3">
-        <v>148500</v>
+        <v>150800</v>
       </c>
       <c r="I17" s="3">
-        <v>143200</v>
+        <v>148300</v>
       </c>
       <c r="J17" s="3">
+        <v>141800</v>
+      </c>
+      <c r="K17" s="3">
         <v>144000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>149200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>142300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>138400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>133200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>120200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>97200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>93400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>90100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>81600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>86800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>97300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>88300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>91600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>91900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>80500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>378100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>81400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>86400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>86700</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>200</v>
       </c>
       <c r="AE17" s="3">
         <v>200</v>
@@ -1619,91 +1646,94 @@
       <c r="AG17" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>61100</v>
+        <v>63900</v>
       </c>
       <c r="E18" s="3">
-        <v>53700</v>
+        <v>61200</v>
       </c>
       <c r="F18" s="3">
-        <v>23300</v>
+        <v>54400</v>
       </c>
       <c r="G18" s="3">
-        <v>57200</v>
+        <v>59100</v>
       </c>
       <c r="H18" s="3">
-        <v>56000</v>
+        <v>59200</v>
       </c>
       <c r="I18" s="3">
-        <v>48700</v>
+        <v>56200</v>
       </c>
       <c r="J18" s="3">
+        <v>50100</v>
+      </c>
+      <c r="K18" s="3">
         <v>42100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>48500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>45200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>32000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>36800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>41900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>31500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>15300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-7000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>19400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>24200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>36600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>18000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>26200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-17500</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-200</v>
       </c>
       <c r="AE18" s="3">
         <v>-200</v>
@@ -1714,8 +1744,11 @@
       <c r="AG18" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,187 +1782,191 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>5300</v>
+        <v>-4300</v>
       </c>
       <c r="E20" s="3">
-        <v>4900</v>
+        <v>-5200</v>
       </c>
       <c r="F20" s="3">
-        <v>-1300</v>
+        <v>-4500</v>
       </c>
       <c r="G20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>6400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>10800</v>
+      </c>
+      <c r="K20" s="3">
+        <v>13300</v>
+      </c>
+      <c r="L20" s="3">
+        <v>4700</v>
+      </c>
+      <c r="M20" s="3">
+        <v>11600</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O20" s="3">
+        <v>3700</v>
+      </c>
+      <c r="P20" s="3">
+        <v>8600</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="R20" s="3">
+        <v>900</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="T20" s="3">
         <v>5000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-13600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>13300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>4700</v>
-      </c>
-      <c r="L20" s="3">
-        <v>11600</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-900</v>
-      </c>
-      <c r="N20" s="3">
-        <v>3700</v>
-      </c>
-      <c r="O20" s="3">
-        <v>8600</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>900</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>5000</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-11200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>18400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-13400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>4400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1300</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>1000</v>
       </c>
       <c r="AE20" s="3">
         <v>1000</v>
       </c>
       <c r="AF20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG20" s="3">
         <v>700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>94900</v>
+      </c>
+      <c r="E21" s="3">
         <v>93900</v>
       </c>
-      <c r="E21" s="3">
-        <v>85500</v>
-      </c>
       <c r="F21" s="3">
-        <v>48200</v>
+        <v>85800</v>
       </c>
       <c r="G21" s="3">
-        <v>89700</v>
+        <v>86700</v>
       </c>
       <c r="H21" s="3">
-        <v>83400</v>
+        <v>91800</v>
       </c>
       <c r="I21" s="3">
-        <v>65400</v>
+        <v>78900</v>
       </c>
       <c r="J21" s="3">
+        <v>69600</v>
+      </c>
+      <c r="K21" s="3">
         <v>88700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>88300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>91300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>66800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>72500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>80000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>51600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>25600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>37700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>49700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>11000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>67100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>39900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>68100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>49800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>49100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>24800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>57900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>42000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2400</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1939,92 +1976,95 @@
       <c r="AG21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E22" s="3">
         <v>18800</v>
       </c>
-      <c r="E22" s="3">
-        <v>19600</v>
-      </c>
       <c r="F22" s="3">
-        <v>20900</v>
+        <v>19200</v>
       </c>
       <c r="G22" s="3">
+        <v>23600</v>
+      </c>
+      <c r="H22" s="3">
         <v>20400</v>
       </c>
-      <c r="H22" s="3">
-        <v>22800</v>
-      </c>
       <c r="I22" s="3">
-        <v>22700</v>
+        <v>18000</v>
       </c>
       <c r="J22" s="3">
-        <v>20300</v>
+        <v>25500</v>
       </c>
       <c r="K22" s="3">
         <v>20300</v>
       </c>
       <c r="L22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="M22" s="3">
         <v>14500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>9600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>14100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>14900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>15700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>16000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>69600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>20300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>19600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>12600</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE22" s="3" t="s">
         <v>5</v>
       </c>
@@ -2034,198 +2074,207 @@
       <c r="AG22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E23" s="3">
         <v>47600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>39000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>41800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>31600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>35000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>33000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>42300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>16900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>28000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>38800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>12900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-11800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>10700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-27700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>25400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>24500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-73200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-28800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E24" s="3">
         <v>13400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-16300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-6600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>500</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG24" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E26" s="3">
         <v>34200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>29100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>30300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>28200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>24600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>29600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>27300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-23700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>22100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>17800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-57000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-22200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E27" s="3">
         <v>34200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>29100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>30300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>28200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>24600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>29600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>27300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-23700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>22100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>17800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-57000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-22200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2669,8 +2730,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -2687,11 +2748,11 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +2956,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5300</v>
+        <v>4300</v>
       </c>
       <c r="E32" s="3">
-        <v>-4900</v>
+        <v>5200</v>
       </c>
       <c r="F32" s="3">
-        <v>1300</v>
+        <v>4500</v>
       </c>
       <c r="G32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H32" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="N32" s="3">
+        <v>900</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>7000</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="S32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T32" s="3">
         <v>-5000</v>
       </c>
-      <c r="H32" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>13600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-13300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-11600</v>
-      </c>
-      <c r="M32" s="3">
-        <v>900</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="P32" s="3">
-        <v>7000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="R32" s="3">
-        <v>1100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>11200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-18400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>13400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AE32" s="3">
         <v>-1000</v>
       </c>
       <c r="AF32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E33" s="3">
         <v>34200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>29100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>30300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>28200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>24600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>29600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>27300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-23700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>22100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>17800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-57000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-22200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E35" s="3">
         <v>34200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>29100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>30300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>28200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>24600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>29600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>27300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-23700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>22100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>17800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-57000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-22200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,126 +3525,130 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>206100</v>
+      </c>
+      <c r="E41" s="3">
         <v>122000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>149500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>136300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>114400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>210100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>64300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>105200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>51600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>86400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>93400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>101300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>128200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>147300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>249600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>120300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>129200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>113200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>113600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>131500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>135600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>92200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>91500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>65000</v>
       </c>
-      <c r="AA41" s="3">
-        <v>0</v>
-      </c>
       <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="3">
         <v>200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3629,142 +3719,148 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>254900</v>
+      </c>
+      <c r="E43" s="3">
         <v>268200</v>
       </c>
-      <c r="E43" s="3">
-        <v>230100</v>
-      </c>
       <c r="F43" s="3">
-        <v>244700</v>
+        <v>225300</v>
       </c>
       <c r="G43" s="3">
-        <v>237600</v>
+        <v>234900</v>
       </c>
       <c r="H43" s="3">
-        <v>221300</v>
+        <v>231800</v>
       </c>
       <c r="I43" s="3">
-        <v>213900</v>
+        <v>269500</v>
       </c>
       <c r="J43" s="3">
+        <v>212400</v>
+      </c>
+      <c r="K43" s="3">
         <v>199200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>215000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>207700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>214800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>195400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>207200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>244100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>213200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>185200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>157500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>138000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>126400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>114500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>129400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>122300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>111600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>100500</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="3" t="s">
-        <v>5</v>
+      <c r="AB43" s="3">
+        <v>0</v>
       </c>
       <c r="AC43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AD43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="3">
         <v>65000</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
-      </c>
       <c r="AF43" s="3">
         <v>0</v>
       </c>
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E44" s="3">
         <v>17200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>17300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>19900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>19800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>18900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>19300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>17900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>16500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>15500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>12100</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3777,8 +3873,8 @@
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
@@ -3819,198 +3915,207 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>42300</v>
+        <v>7600</v>
       </c>
       <c r="E45" s="3">
-        <v>41600</v>
+        <v>6000</v>
       </c>
       <c r="F45" s="3">
-        <v>40500</v>
+        <v>11700</v>
       </c>
       <c r="G45" s="3">
+        <v>16400</v>
+      </c>
+      <c r="H45" s="3">
+        <v>12900</v>
+      </c>
+      <c r="I45" s="3">
+        <v>12300</v>
+      </c>
+      <c r="J45" s="3">
+        <v>6200</v>
+      </c>
+      <c r="K45" s="3">
+        <v>38900</v>
+      </c>
+      <c r="L45" s="3">
+        <v>32900</v>
+      </c>
+      <c r="M45" s="3">
+        <v>37700</v>
+      </c>
+      <c r="N45" s="3">
+        <v>39400</v>
+      </c>
+      <c r="O45" s="3">
         <v>39300</v>
       </c>
-      <c r="H45" s="3">
-        <v>91400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>35400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>38900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>32900</v>
-      </c>
-      <c r="L45" s="3">
-        <v>37700</v>
-      </c>
-      <c r="M45" s="3">
-        <v>39400</v>
-      </c>
-      <c r="N45" s="3">
-        <v>39300</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>36700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>30100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>20000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>22600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>24900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>19400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>26000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>27800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>23200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>20900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>20500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>19600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>17700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>200</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>300</v>
       </c>
       <c r="AG45" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>529000</v>
+      </c>
+      <c r="E46" s="3">
         <v>449600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>438600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>439500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>411300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>542600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>332400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>362600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>317400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>348400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>363000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>348100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>372100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>421600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>482800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>328000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>311600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>270700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>265900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>272400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>288100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>235500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>223600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>185100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>91300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4035,18 +4140,18 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
         <v>3200</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3">
         <v>3700</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4056,8 +4161,8 @@
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -4080,222 +4185,231 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3">
         <v>406000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>404600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>402900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>402700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>402000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>401100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>167500</v>
+      </c>
+      <c r="E48" s="3">
         <v>163700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>158600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>156800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>153100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>151600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>149400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>147400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>141700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>140900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>139300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>134900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>128700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>129000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>97900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>100100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>103700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>104500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>105400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>208900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>69500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>65900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>71700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>69200</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>65400</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1089500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1101700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1118000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1136900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1148600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1171100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1190000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1210900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1227700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1262600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1298000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1326200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>954800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>982200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>905400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>928600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>946900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>968000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>991700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1018600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1008000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1032900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1057400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1079300</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AC49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE49" s="3">
         <v>498200</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4601,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E52" s="3">
         <v>58000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>54700</v>
       </c>
-      <c r="F52" s="3">
-        <v>56800</v>
-      </c>
       <c r="G52" s="3">
+        <v>29300</v>
+      </c>
+      <c r="H52" s="3">
         <v>43100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>39100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>35400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>20500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>27900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>26300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>26500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11100</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
         <v>10000</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4797,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1850600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1773000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1769900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1790000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1756100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1906200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1710900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1756300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1718300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1779900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1824500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1837100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1481900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1559200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1497200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1367300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1372000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1355100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1374100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1407400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1375900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1346500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1365600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1344800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>406200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>405000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>404800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>664900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>402900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>402400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>401800</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,150 +4969,154 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100200</v>
+      </c>
+      <c r="E57" s="3">
         <v>84900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>75600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>78700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>89800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>78400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>71500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>79900</v>
-      </c>
-      <c r="K57" s="3">
-        <v>69100</v>
       </c>
       <c r="L57" s="3">
         <v>69100</v>
       </c>
       <c r="M57" s="3">
+        <v>69100</v>
+      </c>
+      <c r="N57" s="3">
         <v>63000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>67600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>48600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>47400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>41300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>34500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>45600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>36300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>39200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>50800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>57200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>49300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>52200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>45200</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AC57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3">
         <v>20200</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AG57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="F58" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G58" s="3">
+        <v>16200</v>
+      </c>
+      <c r="H58" s="3">
+        <v>16100</v>
+      </c>
+      <c r="I58" s="3">
+        <v>16100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>15900</v>
+      </c>
+      <c r="K58" s="3">
+        <v>21900</v>
+      </c>
+      <c r="L58" s="3">
         <v>9000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>9000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>9000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>9000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>21900</v>
-      </c>
-      <c r="K58" s="3">
-        <v>9000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>12000</v>
       </c>
       <c r="M58" s="3">
         <v>12000</v>
       </c>
       <c r="N58" s="3">
+        <v>12000</v>
+      </c>
+      <c r="O58" s="3">
         <v>37000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>9400</v>
       </c>
       <c r="P58" s="3">
         <v>9400</v>
       </c>
       <c r="Q58" s="3">
+        <v>9400</v>
+      </c>
+      <c r="R58" s="3">
         <v>6500</v>
-      </c>
-      <c r="R58" s="3">
-        <v>9100</v>
       </c>
       <c r="S58" s="3">
         <v>9100</v>
@@ -4994,10 +5128,10 @@
         <v>9100</v>
       </c>
       <c r="V58" s="3">
+        <v>9100</v>
+      </c>
+      <c r="W58" s="3">
         <v>28800</v>
-      </c>
-      <c r="W58" s="3">
-        <v>9100</v>
       </c>
       <c r="X58" s="3">
         <v>9100</v>
@@ -5008,8 +5142,8 @@
       <c r="Z58" s="3">
         <v>9100</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
+      <c r="AA58" s="3">
+        <v>9100</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>5</v>
@@ -5017,285 +5151,294 @@
       <c r="AC58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="3">
         <v>3300</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
-      </c>
       <c r="AF58" s="3">
         <v>0</v>
       </c>
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>90400</v>
+        <v>53100</v>
       </c>
       <c r="E59" s="3">
-        <v>83900</v>
+        <v>48700</v>
       </c>
       <c r="F59" s="3">
-        <v>127000</v>
+        <v>45400</v>
       </c>
       <c r="G59" s="3">
-        <v>98800</v>
+        <v>78100</v>
       </c>
       <c r="H59" s="3">
-        <v>93400</v>
+        <v>53800</v>
       </c>
       <c r="I59" s="3">
-        <v>88100</v>
+        <v>56300</v>
       </c>
       <c r="J59" s="3">
+        <v>52100</v>
+      </c>
+      <c r="K59" s="3">
         <v>85000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>82900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>84400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>79100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>70700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>58900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>49900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>22600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>20400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>19600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>23700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>36100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>24000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>20300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>30400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>10300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>100</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>400</v>
       </c>
       <c r="AG59" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>202500</v>
+      </c>
+      <c r="E60" s="3">
         <v>175300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>159400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>214800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>197600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>180800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>168600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>186800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>161100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>165500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>154100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>175200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>116900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>106700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>70400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>64000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>72000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>65000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>72000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>104900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>90300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>78700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>91800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>68700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>33500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>100</v>
-      </c>
-      <c r="AF60" s="3">
-        <v>400</v>
       </c>
       <c r="AG60" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1036300</v>
+        <v>1064000</v>
       </c>
       <c r="E61" s="3">
-        <v>1037700</v>
+        <v>1063000</v>
       </c>
       <c r="F61" s="3">
-        <v>1029100</v>
+        <v>1065400</v>
       </c>
       <c r="G61" s="3">
-        <v>1030400</v>
+        <v>1058200</v>
       </c>
       <c r="H61" s="3">
-        <v>1129700</v>
+        <v>1060900</v>
       </c>
       <c r="I61" s="3">
-        <v>1140700</v>
+        <v>1162000</v>
       </c>
       <c r="J61" s="3">
+        <v>1174100</v>
+      </c>
+      <c r="K61" s="3">
         <v>1190000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1204000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1205200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1206300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1206800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>965400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>966100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>965900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>832900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>833600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>834300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>835500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>837700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>858200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>859100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>859800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>860200</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5303,93 +5446,96 @@
         <v>0</v>
       </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>425400</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>122700</v>
+        <v>80600</v>
       </c>
       <c r="E62" s="3">
-        <v>123700</v>
+        <v>79200</v>
       </c>
       <c r="F62" s="3">
-        <v>124600</v>
+        <v>78500</v>
       </c>
       <c r="G62" s="3">
-        <v>124100</v>
+        <v>77100</v>
       </c>
       <c r="H62" s="3">
-        <v>130400</v>
+        <v>74500</v>
       </c>
       <c r="I62" s="3">
-        <v>164400</v>
+        <v>77400</v>
       </c>
       <c r="J62" s="3">
+        <v>110200</v>
+      </c>
+      <c r="K62" s="3">
         <v>148300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>158300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>165000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>188200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>195100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>156000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>170000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>152300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>154800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>122400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>124000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>122200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>155200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>99800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>98800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>109200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>113700</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>14000</v>
       </c>
       <c r="AB62" s="3">
         <v>14000</v>
@@ -5398,19 +5544,22 @@
         <v>14000</v>
       </c>
       <c r="AD62" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AE62" s="3">
         <v>73500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>14500</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>14000</v>
       </c>
       <c r="AG62" s="3">
         <v>14000</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5849,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1364000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1334400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1320900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1368500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1352000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1440900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1473800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1525200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1523400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1535600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1548700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1577100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1238300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1242800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1188700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1051800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1028000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1023400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1029700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1097800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1048300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1036600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1060800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1042700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>18900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>17100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>517600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>14700</v>
-      </c>
-      <c r="AF66" s="3">
-        <v>14400</v>
       </c>
       <c r="AG66" s="3">
         <v>14400</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6375,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-71100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-105900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-94900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-125900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-128900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-74400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-93500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-98100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-128200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-90900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-71400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-81400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-100500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-99800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-103800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-94900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-82900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-89600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-74200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-89600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-89400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-107200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-110700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-113300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>18200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6767,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>486500</v>
+      </c>
+      <c r="E76" s="3">
         <v>438600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>449000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>421500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>404100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>465300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>237100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>231100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>194900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>244200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>275800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>260000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>243700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>316400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>308500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>315600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>343900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>331800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>344400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>309600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>327600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>309800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>304800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>302100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>387200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>387900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>389500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>147300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>388200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>388000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>387400</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E81" s="3">
         <v>34200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>29100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>30300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>28200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>24600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>29600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>27300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-23700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>22100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>17800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-57000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-22200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,92 +7202,93 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>27500</v>
+        <v>8600</v>
       </c>
       <c r="E83" s="3">
-        <v>26900</v>
+        <v>9000</v>
       </c>
       <c r="F83" s="3">
-        <v>26200</v>
+        <v>8300</v>
       </c>
       <c r="G83" s="3">
-        <v>27500</v>
+        <v>8200</v>
       </c>
       <c r="H83" s="3">
-        <v>29000</v>
+        <v>8500</v>
       </c>
       <c r="I83" s="3">
-        <v>30300</v>
+        <v>7400</v>
       </c>
       <c r="J83" s="3">
+        <v>8400</v>
+      </c>
+      <c r="K83" s="3">
         <v>33400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>35100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>34500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>35700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>32000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>29500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>27000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>28200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>28700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>29400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>29200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>29300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>29100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>28700</v>
-      </c>
-      <c r="X83" s="3">
-        <v>28900</v>
       </c>
       <c r="Y83" s="3">
         <v>28900</v>
       </c>
       <c r="Z83" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AA83" s="3">
         <v>28500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>28800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>27500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>18600</v>
       </c>
-      <c r="AD83" s="3">
-        <v>0</v>
-      </c>
       <c r="AE83" s="3">
         <v>0</v>
       </c>
@@ -7099,8 +7298,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>108800</v>
+      </c>
+      <c r="E89" s="3">
         <v>40000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>34300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>35700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>62400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>62700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>45200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>69600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>52400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>65100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>31200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>63900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>91800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>28500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>7700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>14800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>38200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>49800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>37400</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
         <v>33500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>11500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,92 +7924,93 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14300</v>
       </c>
-      <c r="F91" s="3">
-        <v>-17000</v>
-      </c>
       <c r="G91" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="H91" s="3">
         <v>-10400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-12200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
@@ -7799,8 +8020,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8216,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-16600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-353600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-111500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-8100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-37500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-559600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-400300</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,31 +8352,32 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,184 +8742,190 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-54600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-146400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>94500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-66600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-73000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-57900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-28700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>263400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-101700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-16900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>123900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6100</v>
-      </c>
-      <c r="S100" s="3">
-        <v>-2400</v>
       </c>
       <c r="T100" s="3">
         <v>-2400</v>
       </c>
       <c r="U100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="V100" s="3">
         <v>-23100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-7400</v>
-      </c>
-      <c r="W100" s="3">
-        <v>-2400</v>
       </c>
       <c r="X100" s="3">
         <v>-2400</v>
       </c>
       <c r="Y100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>31600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>548000</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>401500</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>500</v>
+        <v>-1100</v>
       </c>
       <c r="E101" s="3">
-        <v>-600</v>
+        <v>400</v>
       </c>
       <c r="F101" s="3">
-        <v>1600</v>
+        <v>-300</v>
       </c>
       <c r="G101" s="3">
-        <v>-1100</v>
+        <v>1500</v>
       </c>
       <c r="H101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="J101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="N101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>300</v>
+      </c>
+      <c r="S101" s="3">
+        <v>600</v>
+      </c>
+      <c r="T101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="M101" s="3">
-        <v>2200</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="V101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="W101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>300</v>
-      </c>
-      <c r="R101" s="3">
-        <v>600</v>
-      </c>
-      <c r="S101" s="3">
-        <v>400</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="V101" s="3">
-        <v>1400</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
@@ -8689,99 +8938,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>87800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-27800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-95200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>145700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-41300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>53500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-34900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-26800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-19300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-99900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>129500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>15800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-17300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>43700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>26100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>13400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>22000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>13800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>7400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
   <si>
     <t>VRRM</t>
   </si>
@@ -656,235 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>221500</v>
+      </c>
+      <c r="E8" s="3">
         <v>225600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>222400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>209700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>211000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>209900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>204500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>191900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>186100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>197700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>187500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>170400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>170000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>162100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>128700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>89900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>100200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>96900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>79800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>116700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>112500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>128200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>109600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>98500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>370100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>107600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>98200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>69200</v>
       </c>
-      <c r="AE8" s="3">
-        <v>0</v>
-      </c>
       <c r="AF8" s="3">
         <v>0</v>
       </c>
@@ -894,95 +897,98 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E9" s="3">
         <v>87000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>87400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>80200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>84600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>80900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>76000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>71500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1000</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
@@ -992,95 +998,98 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>134200</v>
+      </c>
+      <c r="E10" s="3">
         <v>138500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>135000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>129500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>126500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>129000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>128500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>120400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>176100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>182200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>175500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>160600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>154000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>151300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>121200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>89000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>94600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>88900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>69700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>106800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>107800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>119600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>105100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>96800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>360900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>104500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>95700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>68200</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1090,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1126,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1224,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,41 +1338,44 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3">
-        <v>35800</v>
-      </c>
       <c r="H14" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-3000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1370,16 +1389,16 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>5300</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1391,26 +1410,26 @@
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>5900</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>26500</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>10200</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1420,95 +1439,98 @@
       <c r="AH14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E15" s="3">
         <v>26700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>27500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>27000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>26200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>27600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>29100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>30300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>34300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>35000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>34900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>35900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>32000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>29500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>27000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>28300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>28800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>29600</v>
-      </c>
-      <c r="U15" s="3">
-        <v>29200</v>
       </c>
       <c r="V15" s="3">
         <v>29200</v>
       </c>
       <c r="W15" s="3">
+        <v>29200</v>
+      </c>
+      <c r="X15" s="3">
         <v>29300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>28700</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>28900</v>
       </c>
       <c r="Z15" s="3">
         <v>28900</v>
       </c>
       <c r="AA15" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AB15" s="3">
         <v>103400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>28800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>27500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>18500</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1518,8 +1540,11 @@
       <c r="AH15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,94 +1576,95 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>167800</v>
+      </c>
+      <c r="E17" s="3">
         <v>161700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>161300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>155400</v>
       </c>
-      <c r="G17" s="3">
-        <v>151900</v>
-      </c>
       <c r="H17" s="3">
+        <v>183400</v>
+      </c>
+      <c r="I17" s="3">
         <v>150800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>148300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>141800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>144000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>149200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>142300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>138400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>133200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>120200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>97200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>93400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>90100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>81600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>86800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>97300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>88300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>91600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>91900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>80500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>378100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>81400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>86400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>86700</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>200</v>
       </c>
       <c r="AF17" s="3">
         <v>200</v>
@@ -1649,94 +1675,97 @@
       <c r="AH17" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E18" s="3">
         <v>63900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>61200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>54400</v>
       </c>
-      <c r="G18" s="3">
-        <v>59100</v>
-      </c>
       <c r="H18" s="3">
+        <v>27600</v>
+      </c>
+      <c r="I18" s="3">
         <v>59200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>56200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>50100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>42100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>48500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>45200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>32000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>36800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>41900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>31500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>15300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>19400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>24200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>36600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>18000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>26200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-17500</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>-200</v>
       </c>
       <c r="AF18" s="3">
         <v>-200</v>
@@ -1747,8 +1776,11 @@
       <c r="AH18" s="3">
         <v>-200</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,193 +1815,197 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>10800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>13300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>11600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-7000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-11200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>18400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-13400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1300</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>1000</v>
       </c>
       <c r="AF20" s="3">
         <v>1000</v>
       </c>
       <c r="AG20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH20" s="3">
         <v>700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>86800</v>
+      </c>
+      <c r="E21" s="3">
         <v>94900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>93900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>85800</v>
       </c>
-      <c r="G21" s="3">
-        <v>86700</v>
-      </c>
       <c r="H21" s="3">
+        <v>55200</v>
+      </c>
+      <c r="I21" s="3">
         <v>91800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>78900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>69600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>88700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>88300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>91300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>66800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>72500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>80000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>51600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>25600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>37700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>49700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>11000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>67100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>39900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>68100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>49800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>49100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>24800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>57900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>42000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2400</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1979,95 +2015,98 @@
       <c r="AH21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E22" s="3">
         <v>19600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>18800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>19200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>23600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>20400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>25500</v>
-      </c>
-      <c r="K22" s="3">
-        <v>20300</v>
       </c>
       <c r="L22" s="3">
         <v>20300</v>
       </c>
       <c r="M22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="N22" s="3">
         <v>14500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>9300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>9500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>14100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>14900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>15700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>16000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>69600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>20300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>19600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>12600</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF22" s="3" t="s">
         <v>5</v>
       </c>
@@ -2077,204 +2116,213 @@
       <c r="AH22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-55900</v>
+      </c>
+      <c r="E23" s="3">
         <v>48500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>47600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>39000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>41800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>31600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>35000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>33000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>42300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>16900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>28000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>38800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>12900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-27700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>25400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>24500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-73200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-28800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E24" s="3">
         <v>13800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-4000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-16300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-6600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>500</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH24" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="E26" s="3">
         <v>34700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>34200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>29100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>30300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>28200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>24600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>29600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>27300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-23700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>22100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>17800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-57000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-22200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="E27" s="3">
         <v>34700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>34200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>29100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>30300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>28200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>24600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>29600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>27300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-23700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>22100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>17800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-57000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-22200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2733,8 +2793,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2751,11 +2811,11 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
@@ -2763,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E32" s="3">
         <v>4300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-10800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-13300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-11600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>7000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>11200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-18400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>13400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AF32" s="3">
         <v>-1000</v>
       </c>
       <c r="AG32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="E33" s="3">
         <v>34700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>34200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>29100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>30300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>28200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>24600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>29600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>27300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-23700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>22100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>17800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-57000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-22200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="E35" s="3">
         <v>34700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>34200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>29100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>30300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>28200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>24600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>29600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>27300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-23700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>22100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>17800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-57000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-22200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,133 +3611,137 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>77600</v>
+      </c>
+      <c r="E41" s="3">
         <v>206100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>122000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>149500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>136300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>114400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>210100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>64300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>105200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>51600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>86400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>93400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>101300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>128200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>147300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>249600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>120300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>129200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>113200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>113600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>131500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>135600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>92200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>91500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>65000</v>
       </c>
-      <c r="AB41" s="3">
-        <v>0</v>
-      </c>
       <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="3">
         <v>200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E42" s="3">
         <v>3200</v>
-      </c>
-      <c r="E42" s="3">
-        <v>2400</v>
       </c>
       <c r="F42" s="3">
         <v>2400</v>
       </c>
       <c r="G42" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H42" s="3">
         <v>2300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1700</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3722,148 +3811,154 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>257800</v>
+      </c>
+      <c r="E43" s="3">
         <v>254900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>268200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>225300</v>
       </c>
-      <c r="G43" s="3">
-        <v>234900</v>
-      </c>
       <c r="H43" s="3">
+        <v>244700</v>
+      </c>
+      <c r="I43" s="3">
         <v>231800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>269500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>212400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>199200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>215000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>207700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>214800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>195400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>207200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>244100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>213200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>185200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>157500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>138000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>126400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>114500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>129400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>122300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>111600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>100500</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC43" s="3" t="s">
-        <v>5</v>
+      <c r="AC43" s="3">
+        <v>0</v>
       </c>
       <c r="AD43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF43" s="3">
         <v>65000</v>
       </c>
-      <c r="AF43" s="3">
-        <v>0</v>
-      </c>
       <c r="AG43" s="3">
         <v>0</v>
       </c>
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E44" s="3">
         <v>18700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>17200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>17300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>18000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>19900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>19800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>18900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>19300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>17900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>16500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>15500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>12100</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3876,8 +3971,8 @@
       <c r="T44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -3918,204 +4013,213 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E45" s="3">
         <v>7600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11700</v>
       </c>
-      <c r="G45" s="3">
-        <v>16400</v>
-      </c>
       <c r="H45" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I45" s="3">
         <v>12900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>38900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>32900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>37700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>39400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>39300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>36700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>30100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>20000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>22600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>24900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>19400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>26000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>27800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>23200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>20900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>20500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>19600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>17700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>200</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>300</v>
       </c>
       <c r="AH45" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>394000</v>
+      </c>
+      <c r="E46" s="3">
         <v>529000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>449600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>438600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>439500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>411300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>542600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>332400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>362600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>317400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>348400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>363000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>348100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>372100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>421600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>482800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>328000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>311600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>270700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>265900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>272400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>288100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>235500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>223600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>185100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>91300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4131,8 +4235,8 @@
       <c r="G47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>5</v>
+      <c r="H47" s="3">
+        <v>600</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>5</v>
@@ -4143,18 +4247,18 @@
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3">
         <v>3200</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O47" s="3">
         <v>3700</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4164,8 +4268,8 @@
       <c r="R47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -4188,228 +4292,237 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB47" s="3">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3">
         <v>406000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>404600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>402900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>402700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>402000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>401100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>171500</v>
+      </c>
+      <c r="E48" s="3">
         <v>167500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>163700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>158600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>156800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>153100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>151600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>149400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>147400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>141700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>140900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>139300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>134900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>128700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>129000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>97900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>100100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>103700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>104500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>105400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>208900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>69500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>65900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>71700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>69200</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>65400</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>967900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1089500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1101700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1118000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1136900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1148600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1171100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1190000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1210900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1227700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1262600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1298000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1326200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>954800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>982200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>905400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>928600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>946900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>968000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>991700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1018600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1008000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1032900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1057400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1079300</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF49" s="3">
         <v>498200</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>81100</v>
+      </c>
+      <c r="E52" s="3">
         <v>64600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>58000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>54700</v>
       </c>
-      <c r="G52" s="3">
-        <v>29300</v>
-      </c>
       <c r="H52" s="3">
+        <v>56200</v>
+      </c>
+      <c r="I52" s="3">
         <v>43100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>40800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>39100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>35400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>28000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>20500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>27900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>26300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>26500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>12900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11100</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>10000</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1614500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1850600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1773000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1769900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1790000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1756100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1906200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1710900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1756300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1718300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1779900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1824500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1837100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1481900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1559200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1497200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1367300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1372000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1355100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1374100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1407400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1375900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1346500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1365600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1344800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>406200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>405000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>404800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>664900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>402900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>402400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>401800</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,156 +5099,160 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>91200</v>
+      </c>
+      <c r="E57" s="3">
         <v>100200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>84900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>75600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>78700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>89800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>78400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>71500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>79900</v>
-      </c>
-      <c r="L57" s="3">
-        <v>69100</v>
       </c>
       <c r="M57" s="3">
         <v>69100</v>
       </c>
       <c r="N57" s="3">
+        <v>69100</v>
+      </c>
+      <c r="O57" s="3">
         <v>63000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>67600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>48600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>47400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>41300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>34500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>45600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>36300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>39200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>50800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>57200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>49300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>52200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>45200</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3">
         <v>20200</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E58" s="3">
         <v>6700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>16200</v>
-      </c>
-      <c r="H58" s="3">
-        <v>16100</v>
       </c>
       <c r="I58" s="3">
         <v>16100</v>
       </c>
       <c r="J58" s="3">
+        <v>16100</v>
+      </c>
+      <c r="K58" s="3">
         <v>15900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>12000</v>
       </c>
       <c r="N58" s="3">
         <v>12000</v>
       </c>
       <c r="O58" s="3">
+        <v>12000</v>
+      </c>
+      <c r="P58" s="3">
         <v>37000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>9400</v>
       </c>
       <c r="Q58" s="3">
         <v>9400</v>
       </c>
       <c r="R58" s="3">
+        <v>9400</v>
+      </c>
+      <c r="S58" s="3">
         <v>6500</v>
-      </c>
-      <c r="S58" s="3">
-        <v>9100</v>
       </c>
       <c r="T58" s="3">
         <v>9100</v>
@@ -5131,10 +5264,10 @@
         <v>9100</v>
       </c>
       <c r="W58" s="3">
+        <v>9100</v>
+      </c>
+      <c r="X58" s="3">
         <v>28800</v>
-      </c>
-      <c r="X58" s="3">
-        <v>9100</v>
       </c>
       <c r="Y58" s="3">
         <v>9100</v>
@@ -5145,8 +5278,8 @@
       <c r="AA58" s="3">
         <v>9100</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
+      <c r="AB58" s="3">
+        <v>9100</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>5</v>
@@ -5154,294 +5287,303 @@
       <c r="AD58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="3">
         <v>3300</v>
       </c>
-      <c r="AF58" s="3">
-        <v>0</v>
-      </c>
       <c r="AG58" s="3">
         <v>0</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E59" s="3">
         <v>53100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>48700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>45400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>78100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>53800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>56300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>52100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>85000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>82900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>84400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>79100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>70700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>58900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>49900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>20400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>19600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>23700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>36100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>24000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>20300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>30400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>14400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>10300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>100</v>
-      </c>
-      <c r="AG59" s="3">
-        <v>400</v>
       </c>
       <c r="AH59" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>199700</v>
+      </c>
+      <c r="E60" s="3">
         <v>202500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>175300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>159400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>214800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>197600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>180800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>168600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>186800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>161100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>165500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>154100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>175200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>116900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>106700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>70400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>64000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>72000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>65000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>72000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>104900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>90300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>78700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>91800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>68700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>33500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>100</v>
-      </c>
-      <c r="AG60" s="3">
-        <v>400</v>
       </c>
       <c r="AH60" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1060000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1064000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1063000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1065400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1058200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1060900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1162000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1174100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1190000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1204000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1205200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1206300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1206800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>965400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>966100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>965900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>832900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>833600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>834300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>835500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>837700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>858200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>859100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>859800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>860200</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5449,96 +5591,99 @@
         <v>0</v>
       </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>425400</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E62" s="3">
         <v>80600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>79200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>78500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>77100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>74500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>77400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>110200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>148300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>158300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>165000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>188200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>195100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>156000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>170000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>152300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>154800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>122400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>124000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>122200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>155200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>99800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>98800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>109200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>113700</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>14000</v>
       </c>
       <c r="AC62" s="3">
         <v>14000</v>
@@ -5547,19 +5692,22 @@
         <v>14000</v>
       </c>
       <c r="AE62" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AF62" s="3">
         <v>73500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>14500</v>
-      </c>
-      <c r="AG62" s="3">
-        <v>14000</v>
       </c>
       <c r="AH62" s="3">
         <v>14000</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1349400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1364000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1334400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1320900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1368500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1352000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1440900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1473800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1525200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1523400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1535600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1548700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1577100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1238300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1242800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1188700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1051800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1028000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1023400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1029700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1097800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1048300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1036600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1060800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1042700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>18900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>17100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>15300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>517600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>14700</v>
-      </c>
-      <c r="AG66" s="3">
-        <v>14400</v>
       </c>
       <c r="AH66" s="3">
         <v>14400</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-269300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-71100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-105900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-94900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-125900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-128900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-74400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-93500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-98100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-128200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-90900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-71400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-81400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-100500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-99800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-103800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-94900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-82900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-89600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-74200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-89600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-89400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-107200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-110700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-113300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>18200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>265100</v>
+      </c>
+      <c r="E76" s="3">
         <v>486500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>438600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>449000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>421500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>404100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>465300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>237100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>231100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>194900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>244200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>275800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>260000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>243700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>316400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>308500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>315600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>343900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>331800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>344400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>309600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>327600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>309800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>304800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>302100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>387200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>387900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>389500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>147300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>388200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>388000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>387400</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="E81" s="3">
         <v>34700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>34200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>29100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>30300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>28200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>24600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>29600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>27300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-23700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>22100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>17800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-57000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-22200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,95 +7400,96 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E83" s="3">
         <v>8600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>33400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>35100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>34500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>35700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>32000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>29500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>27000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>28200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>28700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>29400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>29200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>29300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>29100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>28700</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>28900</v>
       </c>
       <c r="Z83" s="3">
         <v>28900</v>
       </c>
       <c r="AA83" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AB83" s="3">
         <v>28500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>28800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>27500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>18600</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
-      </c>
       <c r="AF83" s="3">
         <v>0</v>
       </c>
@@ -7301,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E89" s="3">
         <v>108800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>40000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>34300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>35700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>62400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>62700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>45200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>69600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>52400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>65100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>31200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>63900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>91800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>28500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>21800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>7700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>14800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>38200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>49800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>37400</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
       <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
         <v>33500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>11500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,95 +8144,96 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-23700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-12200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-8500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
@@ -8023,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-353600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-111500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-8100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-37500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-559600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-400300</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8379,8 +8612,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8451,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,190 +8987,196 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-151900</v>
+      </c>
+      <c r="E100" s="3">
         <v>1300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-54600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-146400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>94500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-66600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-73000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-57900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-28700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>263400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-101700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-16900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>123900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6100</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-2400</v>
       </c>
       <c r="U100" s="3">
         <v>-2400</v>
       </c>
       <c r="V100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="W100" s="3">
         <v>-23100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-7400</v>
-      </c>
-      <c r="X100" s="3">
-        <v>-2400</v>
       </c>
       <c r="Y100" s="3">
         <v>-2400</v>
       </c>
       <c r="Z100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>31600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>548000</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
         <v>0</v>
       </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>401500</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-500</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
         <v>0</v>
       </c>
@@ -8941,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-132100</v>
+      </c>
+      <c r="E102" s="3">
         <v>87800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-27800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>21400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-95200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>145700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-41300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>53500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-34900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-26800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-99900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>129500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-17300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>43700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>26100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>22000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>13800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>7400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>VRRM</t>
   </si>
@@ -656,241 +656,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>223300</v>
+      </c>
+      <c r="E8" s="3">
         <v>221500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>225600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>222400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>209700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>211000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>209900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>204500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>191900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>186100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>197700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>187500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>170400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>170000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>162100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>128700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>89900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>100200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>96900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>79800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>116700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>112500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>128200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>109600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>98500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>370100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>107600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>98200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>69200</v>
       </c>
-      <c r="AF8" s="3">
-        <v>0</v>
-      </c>
       <c r="AG8" s="3">
         <v>0</v>
       </c>
@@ -900,98 +904,101 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E9" s="3">
         <v>87300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>87000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>87400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>80200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>84600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>80900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>76000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>71500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>10100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1000</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1001,98 +1008,101 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>136700</v>
+      </c>
+      <c r="E10" s="3">
         <v>134200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>138500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>135000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>129500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>126500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>129000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>128500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>120400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>176100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>182200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>175500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>160600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>154000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>151300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>121200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>89000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>94600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>88900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>69700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>106800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>107800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>119600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>105100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>96800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>360900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>104500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>95700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>68200</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,44 +1358,47 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>98200</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-3000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1392,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>5300</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1413,26 +1433,26 @@
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>5900</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>26500</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>10200</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1442,98 +1462,101 @@
       <c r="AI14" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E15" s="3">
         <v>27900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>26700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>27500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>27000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>26200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>27600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>29100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>30300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>34300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>35000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>34900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>35900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>32000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>29500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>27000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>28300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>28800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>29600</v>
-      </c>
-      <c r="V15" s="3">
-        <v>29200</v>
       </c>
       <c r="W15" s="3">
         <v>29200</v>
       </c>
       <c r="X15" s="3">
+        <v>29200</v>
+      </c>
+      <c r="Y15" s="3">
         <v>29300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>28700</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>28900</v>
       </c>
       <c r="AA15" s="3">
         <v>28900</v>
       </c>
       <c r="AB15" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AC15" s="3">
         <v>103400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>28800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>27500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>18500</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,97 +1603,98 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>165900</v>
+      </c>
+      <c r="E17" s="3">
         <v>167800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>161700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>161300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>155400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>183400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>150800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>148300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>141800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>144000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>149200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>142300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>138400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>133200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>120200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>97200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>93400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>90100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>81600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>86800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>97300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>88300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>91600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>91900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>80500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>378100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>81400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>86400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>86700</v>
-      </c>
-      <c r="AF17" s="3">
-        <v>200</v>
       </c>
       <c r="AG17" s="3">
         <v>200</v>
@@ -1678,97 +1705,100 @@
       <c r="AI17" s="3">
         <v>200</v>
       </c>
+      <c r="AJ17" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E18" s="3">
         <v>53700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>63900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>61200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>54400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>27600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>59200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>56200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>50100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>42100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>48500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>45200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>32000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>36800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>41900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>31500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>15300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>19400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>24200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>36600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>17700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>18000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>26200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>11800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-17500</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>-200</v>
       </c>
       <c r="AG18" s="3">
         <v>-200</v>
@@ -1779,8 +1809,11 @@
       <c r="AI18" s="3">
         <v>-200</v>
       </c>
+      <c r="AJ18" s="3">
+        <v>-200</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,199 +1849,203 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>10800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>13300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>11600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-11200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>18400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1300</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>1000</v>
       </c>
       <c r="AG20" s="3">
         <v>1000</v>
       </c>
       <c r="AH20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI20" s="3">
         <v>700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>89300</v>
+      </c>
+      <c r="E21" s="3">
         <v>86800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>94900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>93900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>85800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>55200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>91800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>78900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>69600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>88700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>88300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>91300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>66800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>72500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>80000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>51600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>25600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>37700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>49700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>11000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>67100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>39900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>68100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>49800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>49100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>24800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>57900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>42000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2400</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2018,98 +2055,101 @@
       <c r="AI21" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E22" s="3">
         <v>16700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>19600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>18800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>19200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>23600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>20400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>25500</v>
-      </c>
-      <c r="L22" s="3">
-        <v>20300</v>
       </c>
       <c r="M22" s="3">
         <v>20300</v>
       </c>
       <c r="N22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="O22" s="3">
         <v>14500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>9200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>9600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>9500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>12500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>14100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>14900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>15700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>16000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>69600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>20300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>19600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>12600</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG22" s="3" t="s">
         <v>5</v>
       </c>
@@ -2119,210 +2159,219 @@
       <c r="AI22" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ22" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>44800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-55900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>48500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>47600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>39000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>41800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>31600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>35000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>33000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>42300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>16900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>28000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>38800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>12900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>10700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-27700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>25400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>24500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-73200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-28800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E24" s="3">
         <v>10700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>11500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-4000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-16300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-6600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>500</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI24" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ24" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-66700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>34700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>34200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>29100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>30300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>28200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>24600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>29600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>19100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>27300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-23700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>22100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>17800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-57000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-22200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-66700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>34700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>34200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>29100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>30300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>28200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>24600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>29600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>19100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-23700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>22100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>17800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-57000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-22200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2796,8 +2857,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -2814,11 +2875,11 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E32" s="3">
         <v>5300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-10800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-13300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-11600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>11200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-18400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>13400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AG32" s="3">
         <v>-1000</v>
       </c>
       <c r="AH32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-66700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>34700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>34200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>29100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>30300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>28200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>24600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>29600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>19100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>27300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-23700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>22100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>17800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-57000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-22200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-66700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>34700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>34200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>29100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>30300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>28200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>24600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>29600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>19100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>27300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-23700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>22100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>17800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-57000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-22200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,139 +3698,143 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>108500</v>
+      </c>
+      <c r="E41" s="3">
         <v>77600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>206100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>122000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>149500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>136300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>114400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>210100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>64300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>105200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>51600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>86400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>93400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>101300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>128200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>147300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>249600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>120300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>129200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>113200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>113600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>131500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>135600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>92200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>91500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>65000</v>
       </c>
-      <c r="AC41" s="3">
-        <v>0</v>
-      </c>
       <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="3">
         <v>200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3200</v>
-      </c>
-      <c r="F42" s="3">
-        <v>2400</v>
       </c>
       <c r="G42" s="3">
         <v>2400</v>
       </c>
       <c r="H42" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I42" s="3">
         <v>2300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1700</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3814,154 +3904,160 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>258900</v>
+      </c>
+      <c r="E43" s="3">
         <v>257800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>254900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>268200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>225300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>244700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>231800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>269500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>212400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>199200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>215000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>207700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>214800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>195400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>207200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>244100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>213200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>185200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>157500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>138000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>126400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>114500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>129400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>122300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>111600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>100500</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="3" t="s">
-        <v>5</v>
+      <c r="AD43" s="3">
+        <v>0</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG43" s="3">
         <v>65000</v>
       </c>
-      <c r="AG43" s="3">
-        <v>0</v>
-      </c>
       <c r="AH43" s="3">
         <v>0</v>
       </c>
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E44" s="3">
         <v>15500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>18700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>17200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>17300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>18000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>19900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>19800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>18900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>19300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>17900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>16500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>15500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>12100</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3974,8 +4070,8 @@
       <c r="U44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -4016,215 +4112,224 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E45" s="3">
         <v>8100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>32900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>37700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>39400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>39300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>36700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>30100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>20000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>22600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>24900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>19400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>26000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>27800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>23200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>20900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>20500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>19600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>17700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>200</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>300</v>
       </c>
       <c r="AI45" s="3">
         <v>300</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>426100</v>
+      </c>
+      <c r="E46" s="3">
         <v>394000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>529000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>449600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>438600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>439500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>411300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>542600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>332400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>362600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>317400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>348400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>363000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>348100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>372100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>421600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>482800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>328000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>311600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>270700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>265900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>272400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>288100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>235500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>223600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>185100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>91300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
+      <c r="D47" s="3">
+        <v>600</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>5</v>
@@ -4235,12 +4340,12 @@
       <c r="G47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3">
         <v>600</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4250,18 +4355,18 @@
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3">
         <v>3200</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P47" s="3">
         <v>3700</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4271,8 +4376,8 @@
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -4295,234 +4400,243 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
         <v>406000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>404600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>402900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>402700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>402000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>401100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>184100</v>
+      </c>
+      <c r="E48" s="3">
         <v>171500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>167500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>163700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>158600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>156800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>153100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>151600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>149400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>147400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>141700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>140900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>139300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>134900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>128700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>129000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>97900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>100100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>103700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>104500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>105400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>208900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>69500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>65900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>71700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>69200</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
         <v>65400</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>953600</v>
+      </c>
+      <c r="E49" s="3">
         <v>967900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1089500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1101700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1118000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1136900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1148600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1171100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1190000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1210900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1227700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1262600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1298000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1326200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>954800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>982200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>905400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>928600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>946900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>968000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>991700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1018600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1008000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1032900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1057400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1079300</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG49" s="3">
         <v>498200</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E52" s="3">
         <v>81100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>64600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>58000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>54700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>56200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>43100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>40800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>39100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>35400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>28300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>28000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>20500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>27900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>26300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>26500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>12200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>12900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11100</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
         <v>10000</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI52" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1643100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1614500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1850600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1773000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1769900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1790000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1756100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1906200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1710900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1756300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1718300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1779900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1824500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1837100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1481900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1559200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1497200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1367300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1372000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1355100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1374100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1407400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1375900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1346500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1365600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1344800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>406200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>405000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>404800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>664900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>402900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>402400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>401800</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,109 +5230,113 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>89800</v>
+      </c>
+      <c r="E57" s="3">
         <v>91200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>100200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>84900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>75600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>78700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>89800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>78400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>71500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>79900</v>
-      </c>
-      <c r="M57" s="3">
-        <v>69100</v>
       </c>
       <c r="N57" s="3">
         <v>69100</v>
       </c>
       <c r="O57" s="3">
+        <v>69100</v>
+      </c>
+      <c r="P57" s="3">
         <v>63000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>67600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>48600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>47400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>41300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>34500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>45600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>36300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>39200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>50800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>57200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>49300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>52200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>45200</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="3">
         <v>20200</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5210,52 +5344,52 @@
         <v>6900</v>
       </c>
       <c r="E58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F58" s="3">
         <v>6700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>16100</v>
       </c>
       <c r="J58" s="3">
         <v>16100</v>
       </c>
       <c r="K58" s="3">
+        <v>16100</v>
+      </c>
+      <c r="L58" s="3">
         <v>15900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>21900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>12000</v>
       </c>
       <c r="O58" s="3">
         <v>12000</v>
       </c>
       <c r="P58" s="3">
+        <v>12000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>37000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>9400</v>
       </c>
       <c r="R58" s="3">
         <v>9400</v>
       </c>
       <c r="S58" s="3">
+        <v>9400</v>
+      </c>
+      <c r="T58" s="3">
         <v>6500</v>
-      </c>
-      <c r="T58" s="3">
-        <v>9100</v>
       </c>
       <c r="U58" s="3">
         <v>9100</v>
@@ -5267,10 +5401,10 @@
         <v>9100</v>
       </c>
       <c r="X58" s="3">
+        <v>9100</v>
+      </c>
+      <c r="Y58" s="3">
         <v>28800</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>9100</v>
       </c>
       <c r="Z58" s="3">
         <v>9100</v>
@@ -5281,8 +5415,8 @@
       <c r="AB58" s="3">
         <v>9100</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
+      <c r="AC58" s="3">
+        <v>9100</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>5</v>
@@ -5290,303 +5424,312 @@
       <c r="AE58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG58" s="3">
         <v>3300</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
-      </c>
       <c r="AH58" s="3">
         <v>0</v>
       </c>
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E59" s="3">
         <v>48000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>53100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>48700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>45400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>78100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>53800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>56300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>52100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>85000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>82900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>84400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>79100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>70700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>58900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>49900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>20400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>19600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>23700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>36100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>24000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>20300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>30400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>100</v>
-      </c>
-      <c r="AH59" s="3">
-        <v>400</v>
       </c>
       <c r="AI59" s="3">
         <v>400</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>194800</v>
+      </c>
+      <c r="E60" s="3">
         <v>199700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>202500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>175300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>159400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>214800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>197600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>180800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>168600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>186800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>161100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>165500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>154100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>175200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>116900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>106700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>70400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>64000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>72000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>65000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>72000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>104900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>90300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>78700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>91800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>68700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>33500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>100</v>
-      </c>
-      <c r="AH60" s="3">
-        <v>400</v>
       </c>
       <c r="AI60" s="3">
         <v>400</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1058700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1060000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1064000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1063000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1065400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1058200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1060900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1162000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1174100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1190000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1204000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1205200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1206300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1206800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>965400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>966100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>965900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>832900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>833600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>834300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>835500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>837700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>858200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>859100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>859800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>860200</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5594,99 +5737,102 @@
         <v>0</v>
       </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>425400</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E62" s="3">
         <v>75000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>80600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>79200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>78500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>77100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>74500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>77400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>110200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>148300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>158300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>165000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>188200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>195100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>156000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>170000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>152300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>154800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>122400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>124000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>122200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>155200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>99800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>98800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>109200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>113700</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>14000</v>
       </c>
       <c r="AD62" s="3">
         <v>14000</v>
@@ -5695,19 +5841,22 @@
         <v>14000</v>
       </c>
       <c r="AF62" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AG62" s="3">
         <v>73500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>14500</v>
-      </c>
-      <c r="AH62" s="3">
-        <v>14000</v>
       </c>
       <c r="AI62" s="3">
         <v>14000</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>14000</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1343500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1349400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1364000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1334400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1320900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1368500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1352000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1440900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1473800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1525200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1523400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1535600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1548700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1577100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1238300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1242800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1188700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1051800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1028000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1023400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1029700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1097800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1048300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1036600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1060800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1042700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>18900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>17100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>15300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>517600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14700</v>
-      </c>
-      <c r="AH66" s="3">
-        <v>14400</v>
       </c>
       <c r="AI66" s="3">
         <v>14400</v>
       </c>
+      <c r="AJ66" s="3">
+        <v>14400</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-234600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-269300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-71100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-105900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-94900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-125900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-128900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-74400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-93500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-98100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-128200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-90900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-71400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-81400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-100500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-99800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-103800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-94900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-82900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-89600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-74200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-89600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-89400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-107200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-110700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-113300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>18200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>299600</v>
+      </c>
+      <c r="E76" s="3">
         <v>265100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>486500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>438600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>449000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>421500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>404100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>465300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>237100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>231100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>194900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>244200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>275800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>260000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>243700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>316400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>308500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>315600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>343900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>331800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>344400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>309600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>327600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>309800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>304800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>302100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>387200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>387900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>389500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>147300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>388200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>388000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>387400</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-66700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>34700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>34200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>29100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>30300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>28200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>24600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>29600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>19100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>27300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-23700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>22100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>17800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-57000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-22200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,98 +7599,99 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E83" s="3">
         <v>9500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>33400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>35100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>34500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>35700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>32000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>29500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>27000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>28200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>28700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>29400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>29200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>29300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>29100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>28700</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>28900</v>
       </c>
       <c r="AA83" s="3">
         <v>28900</v>
       </c>
       <c r="AB83" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AC83" s="3">
         <v>28500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>28800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>27500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>18600</v>
       </c>
-      <c r="AF83" s="3">
-        <v>0</v>
-      </c>
       <c r="AG83" s="3">
         <v>0</v>
       </c>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E89" s="3">
         <v>40500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>108800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>40000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>34300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>35700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>62400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>62700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>45200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>69600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>52400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>65100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>31200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>63900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>91800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>28500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>21800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>7700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>14800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>38200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>49800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>37400</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
       <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>33500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>11500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,98 +8365,99 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-23700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-18400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-8100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
@@ -8246,8 +8467,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-23400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-353600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-111500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-8100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-37500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-559600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-400300</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8615,8 +8849,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,196 +9233,202 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-151900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-54600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-146400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>94500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-66600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-73000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-57900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-28700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>263400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-101700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-16900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>123900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6100</v>
-      </c>
-      <c r="U100" s="3">
-        <v>-2400</v>
       </c>
       <c r="V100" s="3">
         <v>-2400</v>
       </c>
       <c r="W100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="X100" s="3">
         <v>-23100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-7400</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>-2400</v>
       </c>
       <c r="Z100" s="3">
         <v>-2400</v>
       </c>
       <c r="AA100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>31600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>548000</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>401500</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
         <v>1600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-500</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
         <v>0</v>
       </c>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-132100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>87800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-27800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>21400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-95200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>145700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-41300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>53500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-34900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-26800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-19300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-99900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>129500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-8800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>15800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-17300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>43700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>26100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>13400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>22000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>13800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>7400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t>VRRM</t>
   </si>
@@ -656,248 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>236000</v>
+      </c>
+      <c r="E8" s="3">
         <v>223300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>221500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>225600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>222400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>209700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>211000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>209900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>204500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>191900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>186100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>197700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>187500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>170400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>170000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>162100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>128700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>89900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>100200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>96900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>79800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>116700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>112500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>128200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>109600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>98500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>370100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>107600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>98200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>69200</v>
       </c>
-      <c r="AG8" s="3">
-        <v>0</v>
-      </c>
       <c r="AH8" s="3">
         <v>0</v>
       </c>
@@ -907,101 +911,104 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>94900</v>
+      </c>
+      <c r="E9" s="3">
         <v>86600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>87300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>87000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>87400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>80200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>84600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>80900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>76000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>71500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1000</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1011,101 +1018,104 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>141100</v>
+      </c>
+      <c r="E10" s="3">
         <v>136700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>134200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>138500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>135000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>129500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>126500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>129000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>128500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>120400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>176100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>182200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>175500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>160600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>154000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>151300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>121200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>89000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>94600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>88900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>69700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>106800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>107800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>119600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>105100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>96800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>360900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>104500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>95700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>68200</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1115,8 +1125,11 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1166,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1257,8 +1271,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1378,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1370,38 +1390,38 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>98200</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-3000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1415,16 +1435,16 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>5300</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1436,26 +1456,26 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>5900</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>26500</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>10200</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1465,101 +1485,104 @@
       <c r="AJ14" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E15" s="3">
         <v>27800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>27900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>26700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>27500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>27000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>26200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>27600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>29100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>30300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>34300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>35000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>34900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>35900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>32000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>29500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>27000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>28300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>28800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>29600</v>
-      </c>
-      <c r="W15" s="3">
-        <v>29200</v>
       </c>
       <c r="X15" s="3">
         <v>29200</v>
       </c>
       <c r="Y15" s="3">
+        <v>29200</v>
+      </c>
+      <c r="Z15" s="3">
         <v>29300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>28700</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>28900</v>
       </c>
       <c r="AB15" s="3">
         <v>28900</v>
       </c>
       <c r="AC15" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AD15" s="3">
         <v>103400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>28800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>27500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>18500</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1569,8 +1592,11 @@
       <c r="AJ15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,100 +1630,101 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>172800</v>
+      </c>
+      <c r="E17" s="3">
         <v>165900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>167800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>161700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>161300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>155400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>183400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>150800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>148300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>141800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>144000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>149200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>142300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>138400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>133200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>120200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>97200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>93400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>90100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>81600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>86800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>97300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>88300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>91600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>91900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>80500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>378100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>81400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>86400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>86700</v>
-      </c>
-      <c r="AG17" s="3">
-        <v>200</v>
       </c>
       <c r="AH17" s="3">
         <v>200</v>
@@ -1708,100 +1735,103 @@
       <c r="AJ17" s="3">
         <v>200</v>
       </c>
+      <c r="AK17" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E18" s="3">
         <v>57400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>53700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>63900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>61200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>54400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>27600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>59200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>56200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>50100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>42100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>48500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>45200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>32000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>36800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>41900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>31500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>15300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-7000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>19400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>24200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>36600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>17700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>18000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>26200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>11800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-17500</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>-200</v>
       </c>
       <c r="AH18" s="3">
         <v>-200</v>
@@ -1812,8 +1842,11 @@
       <c r="AJ18" s="3">
         <v>-200</v>
       </c>
+      <c r="AK18" s="3">
+        <v>-200</v>
+      </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,205 +1883,209 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>10800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>13300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>11600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-11200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>18400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1300</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>1000</v>
       </c>
       <c r="AH20" s="3">
         <v>1000</v>
       </c>
       <c r="AI20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>98700</v>
+      </c>
+      <c r="E21" s="3">
         <v>89300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>86800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>94900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>93900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>85800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>55200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>91800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>78900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>69600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>88700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>88300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>91300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>66800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>72500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>80000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>51600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>25600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>37700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>49700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>11000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>67100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>39900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>68100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>49800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>49100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>24800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>57900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>42000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2400</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2058,8 +2095,11 @@
       <c r="AJ21" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2067,92 +2107,92 @@
         <v>16600</v>
       </c>
       <c r="E22" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F22" s="3">
         <v>16700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>19600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>19200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>23600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>18000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>25500</v>
-      </c>
-      <c r="M22" s="3">
-        <v>20300</v>
       </c>
       <c r="N22" s="3">
         <v>20300</v>
       </c>
       <c r="O22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="P22" s="3">
         <v>14500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>14300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>9300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>9600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>14100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>14900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>15700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>16000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>69600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>20300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>19600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>12600</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH22" s="3" t="s">
         <v>5</v>
       </c>
@@ -2162,216 +2202,225 @@
       <c r="AJ22" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK22" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>52600</v>
+      </c>
+      <c r="E23" s="3">
         <v>44800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-55900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>48500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>47600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>39000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>41800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>31600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>35000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>33000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>42300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>16900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>28000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>38800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>12900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>10700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-27700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>25400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>24500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-73200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-28800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E24" s="3">
         <v>12500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-4000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-16300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-6600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>500</v>
       </c>
-      <c r="AI24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ24" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK24" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E26" s="3">
         <v>32300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-66700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>34700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>34200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>29100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>30300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>28200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>24600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>29600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>27300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-23700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>22100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>17800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-57000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>6500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-22200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E27" s="3">
         <v>32300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-66700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>34700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>34200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>29100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>30300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>28200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>24600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>29600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>27300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-23700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>22100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>17800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-57000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>6500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-22200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2860,8 +2921,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -2878,11 +2939,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
@@ -2890,8 +2951,11 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3165,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E32" s="3">
         <v>4100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-10800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-13300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-11600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>11200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-18400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>13400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AH32" s="3">
         <v>-1000</v>
       </c>
       <c r="AI32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E33" s="3">
         <v>32300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-66700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>34700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>34200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>29100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>30300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>28200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>24600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>29600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>27300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-23700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>22100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>17800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-57000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>6500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-22200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E35" s="3">
         <v>32300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-66700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>34700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>34200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>29100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>30300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>28200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>24600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>29600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>27300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-23700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>22100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>17800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-57000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>6500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-22200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,145 +3785,149 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>147700</v>
+      </c>
+      <c r="E41" s="3">
         <v>108500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>77600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>206100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>122000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>149500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>136300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>114400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>210100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>64300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>105200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>51600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>86400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>93400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>101300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>128200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>147300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>249600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>120300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>129200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>113200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>113600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>131500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>135600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>92200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>91500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>65000</v>
       </c>
-      <c r="AD41" s="3">
-        <v>0</v>
-      </c>
       <c r="AE41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="3">
         <v>200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E42" s="3">
         <v>3000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3200</v>
-      </c>
-      <c r="G42" s="3">
-        <v>2400</v>
       </c>
       <c r="H42" s="3">
         <v>2400</v>
       </c>
       <c r="I42" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J42" s="3">
         <v>2300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1700</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -3907,160 +3997,166 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>268800</v>
+      </c>
+      <c r="E43" s="3">
         <v>258900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>257800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>254900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>268200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>225300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>244700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>231800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>269500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>212400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>199200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>215000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>207700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>214800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>195400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>207200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>244100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>213200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>185200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>157500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>138000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>126400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>114500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>129400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>122300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>111600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>100500</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="3" t="s">
-        <v>5</v>
+      <c r="AE43" s="3">
+        <v>0</v>
       </c>
       <c r="AF43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH43" s="3">
         <v>65000</v>
       </c>
-      <c r="AH43" s="3">
-        <v>0</v>
-      </c>
       <c r="AI43" s="3">
         <v>0</v>
       </c>
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E44" s="3">
         <v>16000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>15500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>17200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>17300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>18000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>19900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>19800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>18900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>19300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>17900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>16500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>15500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>12100</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
@@ -4073,8 +4169,8 @@
       <c r="V44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="W44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
@@ -4115,225 +4211,234 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E45" s="3">
         <v>7600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>32900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>37700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>39400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>39300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>36700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>30100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>20000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>22600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>24900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>19400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>26000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>27800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>23200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>20900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>20500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>19600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>17700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>200</v>
-      </c>
-      <c r="AI45" s="3">
-        <v>300</v>
       </c>
       <c r="AJ45" s="3">
         <v>300</v>
       </c>
+      <c r="AK45" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>475100</v>
+      </c>
+      <c r="E46" s="3">
         <v>426100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>394000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>529000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>449600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>438600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>439500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>411300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>542600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>332400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>362600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>317400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>348400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>363000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>348100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>372100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>421600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>482800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>328000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>311600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>270700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>265900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>272400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>288100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>235500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>223600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>185100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>91300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>400</v>
+      </c>
+      <c r="E47" s="3">
         <v>600</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4343,12 +4448,12 @@
       <c r="H47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3">
         <v>600</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4358,18 +4463,18 @@
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O47" s="3">
         <v>3200</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="3">
         <v>3700</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4379,8 +4484,8 @@
       <c r="T47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -4403,240 +4508,249 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD47" s="3">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="3">
         <v>406000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>404600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>402900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>402700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>402000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>401100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E48" s="3">
         <v>184100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>171500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>167500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>163700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>158600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>156800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>153100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>151600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>149400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>147400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>141700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>140900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>139300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>134900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>128700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>129000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>97900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>100100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>103700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>104500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>105400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>208900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>69500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>65900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>71700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>69200</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" s="3">
         <v>65400</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>943300</v>
+      </c>
+      <c r="E49" s="3">
         <v>953600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>967900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1089500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1101700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1118000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1136900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1148600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1171100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1190000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1210900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1227700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1262600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1298000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1326200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>954800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>982200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>905400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>928600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>946900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>968000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>991700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1018600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1008000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1032900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1057400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1079300</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH49" s="3">
         <v>498200</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4960,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E52" s="3">
         <v>78800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>81100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>64600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>58000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>54700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>56200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>43100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>40800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>39100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>35400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>28300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>28000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>20500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>27900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>26300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>26500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>12200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>12900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11100</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3">
         <v>10000</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ52" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5174,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1695400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1643100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1614500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1850600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1773000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1769900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1790000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1756100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1906200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1710900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1756300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1718300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1779900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1824500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1837100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1481900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1559200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1497200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1367300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1372000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1355100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1374100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1407400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1375900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1346500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1365600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1344800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>406200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>405000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>404800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>664900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>402900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>402400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>401800</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,112 +5361,116 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>111400</v>
+      </c>
+      <c r="E57" s="3">
         <v>89800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>91200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>100200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>84900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>75600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>78700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>89800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>78400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>71500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>79900</v>
-      </c>
-      <c r="N57" s="3">
-        <v>69100</v>
       </c>
       <c r="O57" s="3">
         <v>69100</v>
       </c>
       <c r="P57" s="3">
+        <v>69100</v>
+      </c>
+      <c r="Q57" s="3">
         <v>63000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>67600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>48600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>47400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>41300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>34500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>45600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>36300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>39200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>50800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>57200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>49300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>52200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>45200</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="3">
         <v>20200</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5347,52 +5481,52 @@
         <v>6900</v>
       </c>
       <c r="F58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="G58" s="3">
         <v>6700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>16100</v>
       </c>
       <c r="K58" s="3">
         <v>16100</v>
       </c>
       <c r="L58" s="3">
+        <v>16100</v>
+      </c>
+      <c r="M58" s="3">
         <v>15900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>21900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>12000</v>
       </c>
       <c r="P58" s="3">
         <v>12000</v>
       </c>
       <c r="Q58" s="3">
+        <v>12000</v>
+      </c>
+      <c r="R58" s="3">
         <v>37000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>9400</v>
       </c>
       <c r="S58" s="3">
         <v>9400</v>
       </c>
       <c r="T58" s="3">
+        <v>9400</v>
+      </c>
+      <c r="U58" s="3">
         <v>6500</v>
-      </c>
-      <c r="U58" s="3">
-        <v>9100</v>
       </c>
       <c r="V58" s="3">
         <v>9100</v>
@@ -5404,10 +5538,10 @@
         <v>9100</v>
       </c>
       <c r="Y58" s="3">
+        <v>9100</v>
+      </c>
+      <c r="Z58" s="3">
         <v>28800</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>9100</v>
       </c>
       <c r="AA58" s="3">
         <v>9100</v>
@@ -5418,8 +5552,8 @@
       <c r="AC58" s="3">
         <v>9100</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
+      <c r="AD58" s="3">
+        <v>9100</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>5</v>
@@ -5427,312 +5561,321 @@
       <c r="AF58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH58" s="3">
         <v>3300</v>
       </c>
-      <c r="AH58" s="3">
-        <v>0</v>
-      </c>
       <c r="AI58" s="3">
         <v>0</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E59" s="3">
         <v>56600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>48000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>53100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>48700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>45400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>78100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>53800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>56300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>52100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>85000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>82900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>84400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>79100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>70700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>58900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>49900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>22600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>20400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>17300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>19600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>23700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>36100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>24000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>20300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>30400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>100</v>
-      </c>
-      <c r="AI59" s="3">
-        <v>400</v>
       </c>
       <c r="AJ59" s="3">
         <v>400</v>
       </c>
+      <c r="AK59" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>208000</v>
+      </c>
+      <c r="E60" s="3">
         <v>194800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>199700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>202500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>175300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>159400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>214800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>197600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>180800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>168600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>186800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>161100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>165500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>154100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>175200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>116900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>106700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>70400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>64000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>72000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>65000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>72000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>104900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>90300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>78700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>91800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>68700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>33500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>100</v>
-      </c>
-      <c r="AI60" s="3">
-        <v>400</v>
       </c>
       <c r="AJ60" s="3">
         <v>400</v>
       </c>
+      <c r="AK60" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1045700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1058700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1060000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1064000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1063000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1065400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1058200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1060900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1162000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1174100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1190000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1204000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1205200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1206300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1206800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>965400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>966100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>965900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>832900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>833600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>834300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>835500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>837700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>858200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>859100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>859800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>860200</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
@@ -5740,102 +5883,105 @@
         <v>0</v>
       </c>
       <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>425400</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>73900</v>
+      </c>
+      <c r="E62" s="3">
         <v>75500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>75000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>80600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>79200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>78500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>77100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>74500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>77400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>110200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>148300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>158300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>165000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>188200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>195100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>156000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>170000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>152300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>154800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>122400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>124000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>122200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>155200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>99800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>98800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>109200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>113700</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>14000</v>
       </c>
       <c r="AE62" s="3">
         <v>14000</v>
@@ -5844,19 +5990,22 @@
         <v>14000</v>
       </c>
       <c r="AG62" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AH62" s="3">
         <v>73500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>14500</v>
-      </c>
-      <c r="AI62" s="3">
-        <v>14000</v>
       </c>
       <c r="AJ62" s="3">
         <v>14000</v>
       </c>
+      <c r="AK62" s="3">
+        <v>14000</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6322,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1343300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1343500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1349400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1364000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1334400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1320900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1368500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1352000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1440900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1473800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1525200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1523400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1535600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1548700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1577100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1238300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1242800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1188700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1051800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1028000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1023400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1029700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1097800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1048300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1036600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1060800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1042700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>18900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>15300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>517600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14700</v>
-      </c>
-      <c r="AI66" s="3">
-        <v>14400</v>
       </c>
       <c r="AJ66" s="3">
         <v>14400</v>
       </c>
+      <c r="AK66" s="3">
+        <v>14400</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6896,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-196000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-234600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-269300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-71100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-105900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-94900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-125900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-128900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-74400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-93500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-98100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-128200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-90900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-71400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-81400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-100500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-99800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-103800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-94900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-82900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-89600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-74200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-89600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-89400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-107200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-110700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-113300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7324,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>352100</v>
+      </c>
+      <c r="E76" s="3">
         <v>299600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>265100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>486500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>438600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>449000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>421500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>404100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>465300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>237100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>231100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>194900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>244200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>275800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>260000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>243700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>316400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>308500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>315600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>343900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>331800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>344400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>309600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>327600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>309800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>304800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>302100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>387200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>387900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>389500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>147300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>388200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>388000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>387400</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E81" s="3">
         <v>32300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-66700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>34700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>34200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>29100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>30300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>28200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>24600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>29600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>27300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-23700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>22100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>17800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-57000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>6500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-22200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,101 +7798,102 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E83" s="3">
         <v>10200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>33400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>35100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>34500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>35700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>32000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>29500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>27000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>28200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>28700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>29400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>29200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>29300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>29100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>28700</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>28900</v>
       </c>
       <c r="AB83" s="3">
         <v>28900</v>
       </c>
       <c r="AC83" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AD83" s="3">
         <v>28500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>28800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>27500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>18600</v>
       </c>
-      <c r="AG83" s="3">
-        <v>0</v>
-      </c>
       <c r="AH83" s="3">
         <v>0</v>
       </c>
@@ -7704,8 +7903,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>75100</v>
+      </c>
+      <c r="E89" s="3">
         <v>63000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>40500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>108800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>40000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>34300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>35700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>62400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>62700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>45200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>69600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>52400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>65100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>31200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>63900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>91800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>28500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>21800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>14800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>38200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>49800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>37400</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
       <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
         <v>33500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>11500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,101 +8586,102 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-23700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-18400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
@@ -8470,8 +8691,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8905,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-23400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-353600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-111500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-37500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-559600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-400300</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9053,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8852,8 +9086,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8924,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,202 +9479,208 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-151900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-54600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-146400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>94500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-66600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-73000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-57900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-28700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>263400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-101700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-16900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>123900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6100</v>
-      </c>
-      <c r="V100" s="3">
-        <v>-2400</v>
       </c>
       <c r="W100" s="3">
         <v>-2400</v>
       </c>
       <c r="X100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-23100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-7400</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>-2400</v>
       </c>
       <c r="AA100" s="3">
         <v>-2400</v>
       </c>
       <c r="AB100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>31600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>548000</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
         <v>0</v>
       </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>401500</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-500</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
         <v>0</v>
       </c>
@@ -9444,108 +9693,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E102" s="3">
         <v>33400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-132100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>87800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>21400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-95200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>145700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-41300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>53500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-34900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-26800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-19300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-99900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>129500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>15800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-17300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>43700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>26100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>13400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>22000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>13800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>7400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
   <si>
     <t>VRRM</t>
   </si>
@@ -656,262 +656,265 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>257900</v>
+      </c>
+      <c r="E8" s="3">
         <v>261900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>236000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>223300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>221500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>225600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>222400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>209700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>211000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>209900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>204500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>191900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>186100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>197700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>187500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>170400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>170000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>162100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>128700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>89900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>100200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>96900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>79800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>116700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>112500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>128200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>109600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>98500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>370100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>107600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>98200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>69200</v>
       </c>
-      <c r="AI8" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
@@ -921,107 +924,110 @@
       <c r="AL8" s="3">
         <v>0</v>
       </c>
+      <c r="AM8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>115400</v>
+      </c>
+      <c r="E9" s="3">
         <v>110100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>94900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>86600</v>
       </c>
-      <c r="G9" s="3">
-        <v>87300</v>
-      </c>
       <c r="H9" s="3">
+        <v>87200</v>
+      </c>
+      <c r="I9" s="3">
         <v>87000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>87400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>80200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>84600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>80900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>76000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>71500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>10100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>9200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1000</v>
       </c>
-      <c r="AI9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1031,107 +1037,110 @@
       <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>142400</v>
+      </c>
+      <c r="E10" s="3">
         <v>151800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>141100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>136700</v>
       </c>
-      <c r="G10" s="3">
-        <v>134200</v>
-      </c>
       <c r="H10" s="3">
+        <v>134300</v>
+      </c>
+      <c r="I10" s="3">
         <v>138500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>135000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>129500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>126500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>129000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>128500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>120400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>176100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>182200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>175500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>160600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>154000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>151300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>121200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>89000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>94600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>88900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>69700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>106800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>107800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>119600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>105100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>96800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>360900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>104500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>95700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>68200</v>
       </c>
-      <c r="AI10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1141,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1291,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1401,13 +1417,16 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>10600</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1416,38 +1435,38 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>98200</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+        <v>98400</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1300</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1461,16 +1480,16 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>5300</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1482,26 +1501,26 @@
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>5900</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>26500</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>10200</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1511,107 +1530,110 @@
       <c r="AL14" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E15" s="3">
         <v>29300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>29500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>27800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>27900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>26700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>27500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>27000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>26200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>27600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>29100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>30300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>34300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>35000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>34900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>35900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>32000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>29500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>27000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>28300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>28800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>29600</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>29200</v>
       </c>
       <c r="Z15" s="3">
         <v>29200</v>
       </c>
       <c r="AA15" s="3">
+        <v>29200</v>
+      </c>
+      <c r="AB15" s="3">
         <v>29300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>28700</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>28900</v>
       </c>
       <c r="AD15" s="3">
         <v>28900</v>
       </c>
       <c r="AE15" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AF15" s="3">
         <v>103400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>28800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>27500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>18500</v>
       </c>
-      <c r="AI15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1621,8 +1643,11 @@
       <c r="AL15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,106 +1683,107 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>205500</v>
+      </c>
+      <c r="E17" s="3">
         <v>187100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>172800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>165900</v>
       </c>
-      <c r="G17" s="3">
-        <v>167800</v>
-      </c>
       <c r="H17" s="3">
+        <v>167600</v>
+      </c>
+      <c r="I17" s="3">
         <v>161700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>161300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>155400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>183400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>150800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>148300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>141800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>144000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>149200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>142300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>138400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>133200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>120200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>97200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>93400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>90100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>81600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>86800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>97300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>88300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>91600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>91900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>80500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>378100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>81400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>86400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>86700</v>
-      </c>
-      <c r="AI17" s="3">
-        <v>200</v>
       </c>
       <c r="AJ17" s="3">
         <v>200</v>
@@ -1768,106 +1794,109 @@
       <c r="AL17" s="3">
         <v>200</v>
       </c>
+      <c r="AM17" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E18" s="3">
         <v>74800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>63200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>57400</v>
       </c>
-      <c r="G18" s="3">
-        <v>53700</v>
-      </c>
       <c r="H18" s="3">
+        <v>53900</v>
+      </c>
+      <c r="I18" s="3">
         <v>63900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>61200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>54400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>59200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>56200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>50100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>42100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>48500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>45200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>32000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>36800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>41900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>31500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>15300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>19400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>24200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>36600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>17700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>18000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-8000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>26200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>11800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-17500</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>-200</v>
       </c>
       <c r="AJ18" s="3">
         <v>-200</v>
@@ -1878,8 +1907,11 @@
       <c r="AL18" s="3">
         <v>-200</v>
       </c>
+      <c r="AM18" s="3">
+        <v>-200</v>
+      </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1918,217 +1950,221 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>10800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>13300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>11600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>8600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-7000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>5000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>18400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>4400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1300</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>1000</v>
       </c>
       <c r="AJ20" s="3">
         <v>1000</v>
       </c>
       <c r="AK20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AL20" s="3">
         <v>700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>88300</v>
+      </c>
+      <c r="E21" s="3">
         <v>110400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>98700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>89300</v>
       </c>
-      <c r="G21" s="3">
-        <v>86800</v>
-      </c>
       <c r="H21" s="3">
+        <v>87000</v>
+      </c>
+      <c r="I21" s="3">
         <v>94900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>93900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>85800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>55200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>91800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>78900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>69600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>88700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>88300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>91300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>66800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>72500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>80000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>51600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>25600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>37700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>49700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>11000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>67100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>39900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>68100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>49800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>49100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>24800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>57900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>42000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2400</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2138,107 +2174,110 @@
       <c r="AL21" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM21" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E22" s="3">
         <v>16400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>16600</v>
       </c>
       <c r="F22" s="3">
         <v>16600</v>
       </c>
       <c r="G22" s="3">
+        <v>16600</v>
+      </c>
+      <c r="H22" s="3">
         <v>16700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>19600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>19200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>23600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>25500</v>
-      </c>
-      <c r="O22" s="3">
-        <v>20300</v>
       </c>
       <c r="P22" s="3">
         <v>20300</v>
       </c>
       <c r="Q22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="R22" s="3">
         <v>14500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>14300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>9200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>9600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>9500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>12500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>14100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>14900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>15700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>16000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>69600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>20300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>19600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>12600</v>
       </c>
-      <c r="AI22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ22" s="3" t="s">
         <v>5</v>
       </c>
@@ -2248,228 +2287,237 @@
       <c r="AL22" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM22" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E23" s="3">
         <v>64700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>52600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>44800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-55900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>48500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>47600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>39000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>41800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>31600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>35000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>33000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>42300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>16900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>28000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>38800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>12900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>10700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-27700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>25400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>24500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-73200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-28800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E24" s="3">
         <v>17800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>13800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>13400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>11500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-16300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-6600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>500</v>
       </c>
-      <c r="AK24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL24" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM24" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2578,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E26" s="3">
         <v>46800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>38600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>32300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-66700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>34700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>34200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>29100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>30300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>28200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>24600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>29600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>19100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>27300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-23700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>22100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>17800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-57000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-22200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E27" s="3">
         <v>46800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>38600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>32300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-66700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>34700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>34200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>29100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>30300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>28200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>24600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>29600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>19100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>27300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-23700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>22100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>17800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-57000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-22200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2988,8 +3048,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
@@ -3006,11 +3066,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>5</v>
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>5</v>
@@ -3018,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E32" s="3">
         <v>6300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-10800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-13300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-11600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-8600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>7000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>11200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-18400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>13400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AJ32" s="3">
         <v>-1000</v>
       </c>
       <c r="AK32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E33" s="3">
         <v>46800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>38600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>32300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-66700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>34700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>34200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>29100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>30300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>28200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>24600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>29600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>19100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>27300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-23700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>22100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>17800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-57000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-22200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E35" s="3">
         <v>46800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>38600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>32300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-66700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>34700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>34200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>29100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>30300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>28200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>24600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>29600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>19100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>27300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-23700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>22100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>17800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-57000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-22200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,157 +3958,161 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E41" s="3">
         <v>196100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>147700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>108500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>77600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>206100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>122000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>149500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>136300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>114400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>210100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>64300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>105200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>51600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>86400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>93400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>101300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>128200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>147300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>249600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>120300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>129200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>113200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>113600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>131500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>135600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>92200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>91500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>65000</v>
       </c>
-      <c r="AF41" s="3">
-        <v>0</v>
-      </c>
       <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3">
         <v>200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E42" s="3">
         <v>2700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3200</v>
-      </c>
-      <c r="I42" s="3">
-        <v>2400</v>
       </c>
       <c r="J42" s="3">
         <v>2400</v>
       </c>
       <c r="K42" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L42" s="3">
         <v>2300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1700</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4093,172 +4182,178 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>304600</v>
+      </c>
+      <c r="E43" s="3">
         <v>288000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>268800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>258900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>257800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>254900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>268200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>225300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>244700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>231800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>269500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>212400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>199200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>215000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>207700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>214800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>195400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>207200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>244100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>213200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>185200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>157500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>138000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>126400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>114500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>129400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>122300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>111600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>100500</v>
       </c>
-      <c r="AF43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG43" s="3" t="s">
-        <v>5</v>
+      <c r="AG43" s="3">
+        <v>0</v>
       </c>
       <c r="AH43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>65000</v>
       </c>
-      <c r="AJ43" s="3">
-        <v>0</v>
-      </c>
       <c r="AK43" s="3">
         <v>0</v>
       </c>
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E44" s="3">
         <v>21700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>16100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>16000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>15500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>18700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>17200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>17300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>18000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>19900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>19800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>18900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>19300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>17900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>16500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>15500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>12100</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>5</v>
       </c>
@@ -4271,8 +4366,8 @@
       <c r="X44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
@@ -4313,243 +4408,252 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7300</v>
+        <v>11100</v>
       </c>
       <c r="E45" s="3">
         <v>7300</v>
       </c>
       <c r="F45" s="3">
+        <v>7300</v>
+      </c>
+      <c r="G45" s="3">
         <v>7600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>32900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>37700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>39400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>39300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>36700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>30100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>20000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>22600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>24900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>19400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>26000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>27800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>23200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>20900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>20500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>19600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>17700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>200</v>
-      </c>
-      <c r="AK45" s="3">
-        <v>300</v>
       </c>
       <c r="AL45" s="3">
         <v>300</v>
       </c>
+      <c r="AM45" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>440900</v>
+      </c>
+      <c r="E46" s="3">
         <v>557800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>475100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>426100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>394000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>529000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>449600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>438600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>439500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>411300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>542600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>332400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>362600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>317400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>348400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>363000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>348100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>372100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>421600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>482800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>328000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>311600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>270700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>265900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>272400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>288100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>235500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>223600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>185100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>91300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3">
         <v>400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>600</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4559,12 +4663,12 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
         <v>600</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4574,18 +4678,18 @@
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="3">
         <v>3200</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S47" s="3">
         <v>3700</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4595,8 +4699,8 @@
       <c r="V47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -4619,252 +4723,261 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF47" s="3">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG47" s="3">
         <v>406000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>404600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>402900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>402700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>402000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>401100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>245100</v>
+      </c>
+      <c r="E48" s="3">
         <v>231600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>198000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>184100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>171500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>167500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>163700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>158600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>156800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>153100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>151600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>149400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>147400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>141700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>140900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>139300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>134900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>128700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>129000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>97900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>100100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>103700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>104500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>105400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>208900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>69500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>65900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>71700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>69200</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>65400</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>910300</v>
+      </c>
+      <c r="E49" s="3">
         <v>926700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>943300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>953600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>967900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1089500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1101700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1118000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1136900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1148600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1171100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1190000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1210900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1227700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1262600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1298000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1326200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>954800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>982200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>905400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>928600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>946900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>968000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>991700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1018600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1008000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1032900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1057400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1079300</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>498200</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E52" s="3">
         <v>62300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>78600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>78800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>81100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>64600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>58000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>54700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>56200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>43100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>40800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>39100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>35400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>28300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>28000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>20500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>27900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>26300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>26500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>12000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>12200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>12900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>11100</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL52" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1645700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1778300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1695400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1643100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1614500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1850600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1773000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1769900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1790000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1756100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1906200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1710900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1756300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1718300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1779900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1824500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1837100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1481900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1559200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1497200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1367300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1372000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1355100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1374100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1407400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1375900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1346500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1365600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1344800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>406200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>405000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>404800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>664900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>402900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>402400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>401800</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,126 +5622,130 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>101800</v>
+      </c>
+      <c r="E57" s="3">
         <v>122000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>111400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>89800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>91200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>100200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>84900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>75600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>78700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>89800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>78400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>71500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>79900</v>
-      </c>
-      <c r="P57" s="3">
-        <v>69100</v>
       </c>
       <c r="Q57" s="3">
         <v>69100</v>
       </c>
       <c r="R57" s="3">
+        <v>69100</v>
+      </c>
+      <c r="S57" s="3">
         <v>63000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>67600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>48600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>47400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>41300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>34500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>45600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>36300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>39200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>50800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>57200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>49300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>52200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>45200</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AH57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>20200</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AL57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E58" s="3">
         <v>6800</v>
-      </c>
-      <c r="E58" s="3">
-        <v>6900</v>
       </c>
       <c r="F58" s="3">
         <v>6900</v>
@@ -5621,52 +5754,52 @@
         <v>6900</v>
       </c>
       <c r="H58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I58" s="3">
         <v>6700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16200</v>
-      </c>
-      <c r="L58" s="3">
-        <v>16100</v>
       </c>
       <c r="M58" s="3">
         <v>16100</v>
       </c>
       <c r="N58" s="3">
+        <v>16100</v>
+      </c>
+      <c r="O58" s="3">
         <v>15900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>21900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>12000</v>
       </c>
       <c r="R58" s="3">
         <v>12000</v>
       </c>
       <c r="S58" s="3">
+        <v>12000</v>
+      </c>
+      <c r="T58" s="3">
         <v>37000</v>
-      </c>
-      <c r="T58" s="3">
-        <v>9400</v>
       </c>
       <c r="U58" s="3">
         <v>9400</v>
       </c>
       <c r="V58" s="3">
+        <v>9400</v>
+      </c>
+      <c r="W58" s="3">
         <v>6500</v>
-      </c>
-      <c r="W58" s="3">
-        <v>9100</v>
       </c>
       <c r="X58" s="3">
         <v>9100</v>
@@ -5678,10 +5811,10 @@
         <v>9100</v>
       </c>
       <c r="AA58" s="3">
+        <v>9100</v>
+      </c>
+      <c r="AB58" s="3">
         <v>28800</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>9100</v>
       </c>
       <c r="AC58" s="3">
         <v>9100</v>
@@ -5692,8 +5825,8 @@
       <c r="AE58" s="3">
         <v>9100</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>5</v>
+      <c r="AF58" s="3">
+        <v>9100</v>
       </c>
       <c r="AG58" s="3" t="s">
         <v>5</v>
@@ -5701,330 +5834,339 @@
       <c r="AH58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AI58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ58" s="3">
-        <v>0</v>
-      </c>
       <c r="AK58" s="3">
         <v>0</v>
       </c>
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E59" s="3">
         <v>46800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>47400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>56600</v>
       </c>
-      <c r="G59" s="3">
-        <v>48000</v>
-      </c>
       <c r="H59" s="3">
+        <v>48700</v>
+      </c>
+      <c r="I59" s="3">
         <v>53100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>48700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>45400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>78100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>53800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>56300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>52100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>85000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>82900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>84400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>79100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>70700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>58900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>49900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>22600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>20400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>17300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>19600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>23700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>36100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>24000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>20300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>30400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>10300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>100</v>
-      </c>
-      <c r="AK59" s="3">
-        <v>400</v>
       </c>
       <c r="AL59" s="3">
         <v>400</v>
       </c>
+      <c r="AM59" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>210500</v>
+      </c>
+      <c r="E60" s="3">
         <v>227900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>208000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>194800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>199700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>202500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>175300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>159400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>214800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>197600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>180800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>168600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>186800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>161100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>165500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>154100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>175200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>116900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>106700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>70400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>64000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>72000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>65000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>72000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>104900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>90300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>78700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>91800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>68700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>33500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>100</v>
-      </c>
-      <c r="AK60" s="3">
-        <v>400</v>
       </c>
       <c r="AL60" s="3">
         <v>400</v>
       </c>
+      <c r="AM60" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1052500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1059900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1045700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1058700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1060000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1064000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1063000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1065400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1058200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1060900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1162000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1174100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1190000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1204000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1205200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1206300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1206800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>965400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>966100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>965900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>832900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>833600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>834300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>835500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>837700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>858200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>859100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>859800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>860200</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -6032,108 +6174,111 @@
         <v>0</v>
       </c>
       <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>425400</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E62" s="3">
         <v>73300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>73900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>75500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>75000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>80600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>79200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>78500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>77100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>74500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>77400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>110200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>148300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>158300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>165000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>188200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>195100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>156000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>170000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>152300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>154800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>122400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>124000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>122200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>155200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>99800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>98800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>109200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>113700</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>14000</v>
       </c>
       <c r="AG62" s="3">
         <v>14000</v>
@@ -6142,19 +6287,22 @@
         <v>14000</v>
       </c>
       <c r="AI62" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>73500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>14500</v>
-      </c>
-      <c r="AK62" s="3">
-        <v>14000</v>
       </c>
       <c r="AL62" s="3">
         <v>14000</v>
       </c>
+      <c r="AM62" s="3">
+        <v>14000</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6373,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1352700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1375200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1343300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1343500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1349400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1364000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1334400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1320900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1368500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1352000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1440900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1473800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1525200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1523400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1535600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1548700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1577100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1238300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1242800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1188700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1051800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1028000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1023400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1029700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1097800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1048300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1036600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1060800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1042700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>18900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>17100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>15300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>517600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>14700</v>
-      </c>
-      <c r="AK66" s="3">
-        <v>14400</v>
       </c>
       <c r="AL66" s="3">
         <v>14400</v>
       </c>
+      <c r="AM66" s="3">
+        <v>14400</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6963,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-243800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-149200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-196000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-234600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-269300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-71100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-105900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-94900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-125900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-128900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-74400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-93500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-98100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-128200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-90900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-71400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-81400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-100500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-99800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-103800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-94900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-82900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-89600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-74200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-89600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-89400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-107200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-110700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-113300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>18200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>293000</v>
+      </c>
+      <c r="E76" s="3">
         <v>403100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>352100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>299600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>265100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>486500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>438600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>449000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>421500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>404100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>465300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>237100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>231100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>194900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>244200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>275800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>260000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>243700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>316400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>308500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>315600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>343900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>331800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>344400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>309600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>327600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>309800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>304800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>302100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>387200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>387900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>389500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>147300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>388200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>388000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>387400</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E81" s="3">
         <v>46800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>38600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>32300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-66700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>34700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>34200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>29100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>30300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>28200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>24600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>29600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>19100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>27300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-23700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>22100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>17800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-57000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-22200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,107 +8195,108 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E83" s="3">
         <v>9800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>33400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>35100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>34500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>35700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>32000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>29500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>27000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>28200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>28700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>29400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>29200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>29300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>29100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>28700</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>28900</v>
       </c>
       <c r="AD83" s="3">
         <v>28900</v>
       </c>
       <c r="AE83" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AF83" s="3">
         <v>28500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>28800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>27500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>18600</v>
       </c>
-      <c r="AI83" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
@@ -8108,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E89" s="3">
         <v>77700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>75100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>63000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>40500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>108800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>40000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>34300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>35700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>62400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>62700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>45200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>69600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>52400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>65100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>31200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>63900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>91800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>28500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>21800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>7700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>14800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>38200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>49800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>37400</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
       <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
         <v>33500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>11500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,107 +9027,108 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-28800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-34900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-21200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-23700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-14100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-14300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-18400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-5900</v>
       </c>
-      <c r="AI91" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
@@ -8918,8 +9138,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-34800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-23400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-353600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-111500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-37500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-559600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-400300</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9326,8 +9559,8 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9398,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,214 +9970,220 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-137700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-151900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-54600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-146400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>94500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-66600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-57900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-28700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>263400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-101700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-16900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>123900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6100</v>
-      </c>
-      <c r="X100" s="3">
-        <v>-2400</v>
       </c>
       <c r="Y100" s="3">
         <v>-2400</v>
       </c>
       <c r="Z100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-23100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-7400</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>-2400</v>
       </c>
       <c r="AC100" s="3">
         <v>-2400</v>
       </c>
       <c r="AD100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>31600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>548000</v>
       </c>
-      <c r="AI100" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
       <c r="AK100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>401500</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-500</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
       <c r="AI101" s="3">
         <v>0</v>
       </c>
@@ -9948,114 +10196,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-132000</v>
+      </c>
+      <c r="E102" s="3">
         <v>46400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>39400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>33400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-132100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>87800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-27800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>21400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-95200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>145700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-41300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>53500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-34900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-26800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-19300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-99900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>129500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-8800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>15800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-17300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>43700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>26100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>13400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>22000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>13800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>7400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
   <si>
     <t>VRRM</t>
   </si>
@@ -656,268 +656,272 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>223600</v>
+      </c>
+      <c r="E8" s="3">
         <v>257900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>261900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>236000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>223300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>221500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>225600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>222400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>209700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>211000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>209900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>204500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>191900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>186100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>197700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>187500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>170400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>170000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>162100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>128700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>89900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>100200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>96900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>79800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>116700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>112500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>128200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>109600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>98500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>370100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>107600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>98200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>69200</v>
       </c>
-      <c r="AJ8" s="3">
-        <v>0</v>
-      </c>
       <c r="AK8" s="3">
         <v>0</v>
       </c>
@@ -927,110 +931,113 @@
       <c r="AM8" s="3">
         <v>0</v>
       </c>
+      <c r="AN8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>101600</v>
+      </c>
+      <c r="E9" s="3">
         <v>115400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>110100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>94900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>86600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>87200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>87000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>87400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>80200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>84600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>80900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>76000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>71500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>10100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>9200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1040,110 +1047,113 @@
       <c r="AM9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>121900</v>
+      </c>
+      <c r="E10" s="3">
         <v>142400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>151800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>141100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>136700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>134300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>138500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>135000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>129500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>126500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>129000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>128500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>120400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>176100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>182200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>175500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>160600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>154000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>151300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>121200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>89000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>94600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>88900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>69700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>106800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>107800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>119600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>105100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>96800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>360900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>104500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>95700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>68200</v>
       </c>
-      <c r="AJ10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1153,8 +1163,11 @@
       <c r="AM10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1194,8 +1207,9 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1307,8 +1321,11 @@
       <c r="AM12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1420,17 +1437,20 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>10600</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
@@ -1438,38 +1458,38 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>98400</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1300</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-3000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1483,16 +1503,16 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>5300</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1504,26 +1524,26 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>5900</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>26500</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1533,110 +1553,113 @@
       <c r="AM14" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN14" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E15" s="3">
         <v>29800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>29300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>29500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>27800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>27900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>26700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>27500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>27000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>26200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>27600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>29100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>30300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>34300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>35000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>34900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>35900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>32000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>29500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>27000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>28300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>28800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>29600</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>29200</v>
       </c>
       <c r="AA15" s="3">
         <v>29200</v>
       </c>
       <c r="AB15" s="3">
+        <v>29200</v>
+      </c>
+      <c r="AC15" s="3">
         <v>29300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>28700</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>28900</v>
       </c>
       <c r="AE15" s="3">
         <v>28900</v>
       </c>
       <c r="AF15" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AG15" s="3">
         <v>103400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>28800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>27500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>18500</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1646,8 +1669,11 @@
       <c r="AM15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,109 +1710,110 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>171800</v>
+      </c>
+      <c r="E17" s="3">
         <v>205500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>187100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>172800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>165900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>167600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>161700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>161300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>155400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>183400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>150800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>148300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>141800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>144000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>149200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>142300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>138400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>133200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>120200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>97200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>93400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>90100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>81600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>86800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>97300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>88300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>91600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>91900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>80500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>378100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>81400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>86400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>86700</v>
-      </c>
-      <c r="AJ17" s="3">
-        <v>200</v>
       </c>
       <c r="AK17" s="3">
         <v>200</v>
@@ -1797,109 +1824,112 @@
       <c r="AM17" s="3">
         <v>200</v>
       </c>
+      <c r="AN17" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E18" s="3">
         <v>52400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>74800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>63200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>57400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>53900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>63900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>61200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>54400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>27600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>59200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>56200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>50100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>42100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>48500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>45200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>32000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>36800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>41900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>31500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>15300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>19400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>24200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>36600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>17700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>18000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-8000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>26200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>11800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-17500</v>
-      </c>
-      <c r="AJ18" s="3">
-        <v>-200</v>
       </c>
       <c r="AK18" s="3">
         <v>-200</v>
@@ -1910,8 +1940,11 @@
       <c r="AM18" s="3">
         <v>-200</v>
       </c>
+      <c r="AN18" s="3">
+        <v>-200</v>
+      </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1951,223 +1984,227 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>10800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>13300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>11600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>8600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>5000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>18400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-13400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>4400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1300</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>1000</v>
       </c>
       <c r="AK20" s="3">
         <v>1000</v>
       </c>
       <c r="AL20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AM20" s="3">
         <v>700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>85200</v>
+      </c>
+      <c r="E21" s="3">
         <v>88300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>110400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>98700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>89300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>87000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>94900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>93900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>85800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>55200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>91800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>78900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>69600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>88700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>88300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>91300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>66800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>72500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>80000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>51600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>25600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>37700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>49700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>11000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>67100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>39900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>68100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>49800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>49100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>24800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>57900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>42000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2177,110 +2214,113 @@
       <c r="AM21" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN21" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E22" s="3">
         <v>15000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>16600</v>
       </c>
       <c r="G22" s="3">
         <v>16600</v>
       </c>
       <c r="H22" s="3">
+        <v>16600</v>
+      </c>
+      <c r="I22" s="3">
         <v>16700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>19600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>19200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>23600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>18000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>25500</v>
-      </c>
-      <c r="P22" s="3">
-        <v>20300</v>
       </c>
       <c r="Q22" s="3">
         <v>20300</v>
       </c>
       <c r="R22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="S22" s="3">
         <v>14500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>14300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>11700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>9300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>9600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>12500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>14100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>14900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>15700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>16000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>69600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>20300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>19600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>12600</v>
       </c>
-      <c r="AJ22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK22" s="3" t="s">
         <v>5</v>
       </c>
@@ -2290,234 +2330,243 @@
       <c r="AM22" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN22" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E23" s="3">
         <v>32900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>64700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>52600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>44800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-55900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>48500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>47600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>39000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>41800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>31600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>35000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>33000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>42300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>16900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>28000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>38800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>12900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>10700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-27700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>25400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>24500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-73200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>8800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-28800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E24" s="3">
         <v>14000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>17800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>10700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>13800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>13400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>11500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-16300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-6600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>500</v>
       </c>
-      <c r="AL24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM24" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN24" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2629,234 +2678,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E26" s="3">
         <v>18900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>46800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>38600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>32300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-66700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>34700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>34200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>29100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>30300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>28200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>24600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>29600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>19100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>27300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-23700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>22100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>17800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-57000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-22200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E27" s="3">
         <v>18900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>46800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>38600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>32300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-66700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>34700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>34200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>29100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>30300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>28200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>24600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>29600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>19100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>27300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-23700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>22100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>17800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-57000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>6500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-22200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2968,8 +3026,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3051,8 +3112,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
@@ -3069,11 +3130,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>5</v>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>5</v>
@@ -3081,8 +3142,11 @@
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3194,8 +3258,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3307,234 +3374,243 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E32" s="3">
         <v>6100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-10800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-11600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-8600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>11200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-18400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>13400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AK32" s="3">
         <v>-1000</v>
       </c>
       <c r="AL32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AM32" s="3">
         <v>-700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E33" s="3">
         <v>18900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>46800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>38600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>32300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-66700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>34700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>34200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>29100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>30300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>28200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>24600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>29600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>19100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>27300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-23700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>22100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>17800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-57000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-22200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3646,239 +3722,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E35" s="3">
         <v>18900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>46800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>38600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>32300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-66700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>34700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>34200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>29100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>30300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>28200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>24600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>29600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>19100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>27300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-23700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>22100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>17800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-57000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-22200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3918,8 +4003,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3959,163 +4045,167 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E41" s="3">
         <v>65300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>196100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>147700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>108500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>77600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>206100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>122000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>149500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>136300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>114400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>210100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>64300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>105200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>51600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>86400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>93400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>101300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>128200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>147300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>249600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>120300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>129200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>113200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>113600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>131500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>135600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>92200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>91500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>65000</v>
       </c>
-      <c r="AG41" s="3">
-        <v>0</v>
-      </c>
       <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3">
         <v>200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E42" s="3">
         <v>3100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3200</v>
-      </c>
-      <c r="J42" s="3">
-        <v>2400</v>
       </c>
       <c r="K42" s="3">
         <v>2400</v>
       </c>
       <c r="L42" s="3">
+        <v>2400</v>
+      </c>
+      <c r="M42" s="3">
         <v>2300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1700</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4185,178 +4275,184 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>314900</v>
+      </c>
+      <c r="E43" s="3">
         <v>304600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>288000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>268800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>258900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>257800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>254900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>268200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>225300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>244700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>231800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>269500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>212400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>199200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>215000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>207700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>214800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>195400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>207200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>244100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>213200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>185200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>157500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>138000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>126400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>114500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>129400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>122300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>111600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>100500</v>
       </c>
-      <c r="AG43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="3" t="s">
-        <v>5</v>
+      <c r="AH43" s="3">
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AJ43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK43" s="3">
         <v>65000</v>
       </c>
-      <c r="AK43" s="3">
-        <v>0</v>
-      </c>
       <c r="AL43" s="3">
         <v>0</v>
       </c>
       <c r="AM43" s="3">
         <v>0</v>
       </c>
+      <c r="AN43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E44" s="3">
         <v>20700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>21700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>16100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>16000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>15500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>18700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>17200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>17300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>18000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>19900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>19800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>18900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>19300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>17900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>16500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>15500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>12100</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>5</v>
       </c>
@@ -4369,8 +4465,8 @@
       <c r="Y44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z44" s="3">
-        <v>0</v>
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA44" s="3">
         <v>0</v>
@@ -4411,234 +4507,243 @@
       <c r="AM44" s="3">
         <v>0</v>
       </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E45" s="3">
         <v>11100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>7300</v>
       </c>
       <c r="F45" s="3">
         <v>7300</v>
       </c>
       <c r="G45" s="3">
+        <v>7300</v>
+      </c>
+      <c r="H45" s="3">
         <v>7600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>38900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>32900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>37700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>39400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>39300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>36700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>30100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>20000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>22600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>24900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>19400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>26000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>27800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>23200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>20900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>20500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>19600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>17700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>200</v>
-      </c>
-      <c r="AL45" s="3">
-        <v>300</v>
       </c>
       <c r="AM45" s="3">
         <v>300</v>
       </c>
+      <c r="AN45" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>438900</v>
+      </c>
+      <c r="E46" s="3">
         <v>440900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>557800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>475100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>426100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>394000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>529000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>449600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>438600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>439500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>411300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>542600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>332400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>362600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>317400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>348400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>363000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>348100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>372100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>421600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>482800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>328000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>311600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>270700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>265900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>272400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>288100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>235500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>223600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>185100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>91300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4648,15 +4753,15 @@
       <c r="E47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3">
         <v>400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>600</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4666,12 +4771,12 @@
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3">
         <v>600</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4681,18 +4786,18 @@
       <c r="P47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R47" s="3">
         <v>3200</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T47" s="3">
         <v>3700</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4702,8 +4807,8 @@
       <c r="W47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -4726,258 +4831,267 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH47" s="3">
         <v>406000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>404600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>402900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>402700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>402000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>401100</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>269700</v>
+      </c>
+      <c r="E48" s="3">
         <v>245100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>231600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>198000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>184100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>171500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>167500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>163700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>158600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>156800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>153100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>151600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>149400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>147400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>141700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>140900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>139300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>134900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>128700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>129000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>97900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>100100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>103700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>104500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>105400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>208900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>69500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>65900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>71700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>69200</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AJ48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK48" s="3">
         <v>65400</v>
       </c>
-      <c r="AK48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AM48" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN48" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>894500</v>
+      </c>
+      <c r="E49" s="3">
         <v>910300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>926700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>943300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>953600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>967900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1089500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1101700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1118000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1136900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1148600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1171100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1190000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1210900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1227700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1262600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1298000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1326200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>954800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>982200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>905400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>928600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>946900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>968000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>991700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1018600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1008000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1032900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1057400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1079300</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AJ49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK49" s="3">
         <v>498200</v>
       </c>
-      <c r="AK49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AM49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5089,8 +5203,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5202,121 +5319,127 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E52" s="3">
         <v>49400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>62300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>78600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>78800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>81100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>64600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>58000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>54700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>56200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>43100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>40800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>39100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>35400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>28300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>28000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>20500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>27900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>26300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>26500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>12000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>12200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>12900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11100</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AJ52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK52" s="3">
         <v>10000</v>
       </c>
-      <c r="AK52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AM52" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN52" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5428,121 +5551,127 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1656000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1645700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1778300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1695400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1643100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1614500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1850600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1773000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1769900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1790000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1756100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1906200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1710900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1756300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1718300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1779900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1824500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1837100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1481900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1559200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1497200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1367300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1372000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1355100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1374100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1407400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1375900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1346500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1365600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1344800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>406200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>405000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>404800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>664900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>402900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>402400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>401800</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5582,8 +5711,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5623,132 +5753,136 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>114300</v>
+      </c>
+      <c r="E57" s="3">
         <v>101800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>122000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>111400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>89800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>91200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>100200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>84900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>75600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>78700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>89800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>78400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>71500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>79900</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>69100</v>
       </c>
       <c r="R57" s="3">
         <v>69100</v>
       </c>
       <c r="S57" s="3">
+        <v>69100</v>
+      </c>
+      <c r="T57" s="3">
         <v>63000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>67600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>48600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>47400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>41300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>34500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>45600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>36300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>39200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>50800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>57200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>49300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>52200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>45200</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AJ57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK57" s="3">
         <v>20200</v>
       </c>
-      <c r="AK57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AM57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E58" s="3">
         <v>13600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>6900</v>
       </c>
       <c r="G58" s="3">
         <v>6900</v>
@@ -5757,52 +5891,52 @@
         <v>6900</v>
       </c>
       <c r="I58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="J58" s="3">
         <v>6700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>16200</v>
-      </c>
-      <c r="M58" s="3">
-        <v>16100</v>
       </c>
       <c r="N58" s="3">
         <v>16100</v>
       </c>
       <c r="O58" s="3">
+        <v>16100</v>
+      </c>
+      <c r="P58" s="3">
         <v>15900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>21900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>9000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>12000</v>
       </c>
       <c r="S58" s="3">
         <v>12000</v>
       </c>
       <c r="T58" s="3">
+        <v>12000</v>
+      </c>
+      <c r="U58" s="3">
         <v>37000</v>
-      </c>
-      <c r="U58" s="3">
-        <v>9400</v>
       </c>
       <c r="V58" s="3">
         <v>9400</v>
       </c>
       <c r="W58" s="3">
+        <v>9400</v>
+      </c>
+      <c r="X58" s="3">
         <v>6500</v>
-      </c>
-      <c r="X58" s="3">
-        <v>9100</v>
       </c>
       <c r="Y58" s="3">
         <v>9100</v>
@@ -5814,10 +5948,10 @@
         <v>9100</v>
       </c>
       <c r="AB58" s="3">
+        <v>9100</v>
+      </c>
+      <c r="AC58" s="3">
         <v>28800</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>9100</v>
       </c>
       <c r="AD58" s="3">
         <v>9100</v>
@@ -5828,8 +5962,8 @@
       <c r="AF58" s="3">
         <v>9100</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
+      <c r="AG58" s="3">
+        <v>9100</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>5</v>
@@ -5837,339 +5971,348 @@
       <c r="AI58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AJ58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK58" s="3">
         <v>3300</v>
       </c>
-      <c r="AK58" s="3">
-        <v>0</v>
-      </c>
       <c r="AL58" s="3">
         <v>0</v>
       </c>
       <c r="AM58" s="3">
         <v>0</v>
       </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E59" s="3">
         <v>41100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>46800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>47400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>56600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>48700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>53100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>48700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>45400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>78100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>53800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>56300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>52100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>85000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>82900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>84400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>79100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>70700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>58900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>49900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>22600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>20400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>17300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>19600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>23700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>36100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>24000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>20300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>30400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>14400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>10300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>100</v>
-      </c>
-      <c r="AL59" s="3">
-        <v>400</v>
       </c>
       <c r="AM59" s="3">
         <v>400</v>
       </c>
+      <c r="AN59" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>231900</v>
+      </c>
+      <c r="E60" s="3">
         <v>210500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>227900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>208000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>194800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>199700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>202500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>175300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>159400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>214800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>197600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>180800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>168600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>186800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>161100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>165500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>154100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>175200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>116900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>106700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>70400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>64000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>72000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>65000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>72000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>104900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>90300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>78700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>91800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>68700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>33500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>100</v>
-      </c>
-      <c r="AL60" s="3">
-        <v>400</v>
       </c>
       <c r="AM60" s="3">
         <v>400</v>
       </c>
+      <c r="AN60" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1061000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1052500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1059900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1045700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1058700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1060000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1064000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1063000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1065400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1058200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1060900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1162000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1174100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1190000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1204000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1205200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1206300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1206800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>965400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>966100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>965900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>832900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>833600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>834300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>835500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>837700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>858200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>859100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>859800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>860200</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
@@ -6177,111 +6320,114 @@
         <v>0</v>
       </c>
       <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
         <v>425400</v>
       </c>
-      <c r="AK61" s="3">
-        <v>0</v>
-      </c>
       <c r="AL61" s="3">
         <v>0</v>
       </c>
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>75200</v>
+      </c>
+      <c r="E62" s="3">
         <v>73400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>73300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>73900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>75500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>75000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>80600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>79200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>78500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>77100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>74500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>77400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>110200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>148300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>158300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>165000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>188200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>195100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>156000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>170000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>152300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>154800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>122400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>124000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>122200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>155200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>99800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>98800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>109200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>113700</v>
-      </c>
-      <c r="AG62" s="3">
-        <v>14000</v>
       </c>
       <c r="AH62" s="3">
         <v>14000</v>
@@ -6290,19 +6436,22 @@
         <v>14000</v>
       </c>
       <c r="AJ62" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AK62" s="3">
         <v>73500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>14500</v>
-      </c>
-      <c r="AL62" s="3">
-        <v>14000</v>
       </c>
       <c r="AM62" s="3">
         <v>14000</v>
       </c>
+      <c r="AN62" s="3">
+        <v>14000</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6414,8 +6563,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6527,8 +6679,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6640,121 +6795,127 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1384000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1352700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1375200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1343300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1343500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1349400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1364000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1334400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1320900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1368500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1352000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1440900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1473800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1525200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1523400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1535600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1548700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1577100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1238300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1242800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1188700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1051800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1028000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1023400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1029700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1097800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1048300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1036600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1060800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1042700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>18900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>17100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>15300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>517600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>14700</v>
-      </c>
-      <c r="AL66" s="3">
-        <v>14400</v>
       </c>
       <c r="AM66" s="3">
         <v>14400</v>
       </c>
+      <c r="AN66" s="3">
+        <v>14400</v>
+      </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6794,8 +6955,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6907,8 +7069,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7020,8 +7185,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7133,8 +7301,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7246,121 +7417,127 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-259900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-243800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-149200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-196000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-234600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-269300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-71100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-105900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-94900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-125900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-128900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-74400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-93500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-98100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-128200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-90900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-71400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-81400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-100500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-99800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-103800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-94900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-82900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-89600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-74200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-89600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-89400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-107200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-110700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-113300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>18200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7472,8 +7649,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7585,8 +7765,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7698,121 +7881,127 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>272000</v>
+      </c>
+      <c r="E76" s="3">
         <v>293000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>403100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>352100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>299600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>265100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>486500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>438600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>449000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>421500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>404100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>465300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>237100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>231100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>194900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>244200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>275800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>260000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>243700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>316400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>308500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>315600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>343900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>331800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>344400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>309600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>327600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>309800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>304800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>302100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>387200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>387900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>389500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>147300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>388200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>388000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>387400</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7924,239 +8113,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E81" s="3">
         <v>18900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>46800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>38600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>32300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-66700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>34700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>34200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>29100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>30300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>28200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>24600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>29600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>19100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>27300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-23700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>22100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>17800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-57000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-22200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8196,8 +8394,9 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8205,101 +8404,101 @@
         <v>10800</v>
       </c>
       <c r="E83" s="3">
+        <v>10800</v>
+      </c>
+      <c r="F83" s="3">
         <v>9800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>33400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>35100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>34500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>35700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>32000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>29500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>27000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>28200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>28700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>29400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>29200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>29300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>29100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>28700</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>28900</v>
       </c>
       <c r="AE83" s="3">
         <v>28900</v>
       </c>
       <c r="AF83" s="3">
+        <v>28900</v>
+      </c>
+      <c r="AG83" s="3">
         <v>28500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>28800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>27500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>18600</v>
       </c>
-      <c r="AJ83" s="3">
-        <v>0</v>
-      </c>
       <c r="AK83" s="3">
         <v>0</v>
       </c>
@@ -8309,8 +8508,11 @@
       <c r="AM83" s="3">
         <v>0</v>
       </c>
+      <c r="AN83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8422,8 +8624,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8535,8 +8740,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8648,8 +8856,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8761,8 +8972,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8874,121 +9088,127 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E89" s="3">
         <v>40000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>77700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>75100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>63000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>40500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>108800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>40000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>34300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>35700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>62400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>62700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>45200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>69600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>52400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>65100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>31200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>63900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>91800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>28500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>21800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>7700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>14800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>38200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>49800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>37400</v>
       </c>
-      <c r="AF89" s="3">
-        <v>0</v>
-      </c>
       <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3">
         <v>33500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>11500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9028,110 +9248,111 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-34200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-28800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-34900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-21200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-23700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-14100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-18400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-5900</v>
       </c>
-      <c r="AJ91" s="3">
-        <v>0</v>
-      </c>
       <c r="AK91" s="3">
         <v>0</v>
       </c>
@@ -9141,8 +9362,11 @@
       <c r="AM91" s="3">
         <v>0</v>
       </c>
+      <c r="AN91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9254,8 +9478,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9367,121 +9594,127 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-34100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-28600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-34800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-23400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-353600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-111500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-8100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-37500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-559600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-400300</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9521,8 +9754,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9562,8 +9796,8 @@
       <c r="O96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9634,8 +9868,11 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9747,8 +9984,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9860,8 +10100,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9973,220 +10216,226 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-137700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-151900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-54600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-146400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>94500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-66600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-73000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-57900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-28700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>263400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-101700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-16900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>123900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6100</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>-2400</v>
       </c>
       <c r="Z100" s="3">
         <v>-2400</v>
       </c>
       <c r="AA100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-23100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-7400</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>-2400</v>
       </c>
       <c r="AD100" s="3">
         <v>-2400</v>
       </c>
       <c r="AE100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>31600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>548000</v>
       </c>
-      <c r="AJ100" s="3">
-        <v>0</v>
-      </c>
       <c r="AK100" s="3">
         <v>0</v>
       </c>
       <c r="AL100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM100" s="3">
         <v>-400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>401500</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-500</v>
       </c>
-      <c r="AI101" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
@@ -10199,117 +10448,123 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-132000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>46400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>39400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>33400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-132100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>87800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-27800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>21400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-95200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>145700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-41300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>53500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-34900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-26800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-19300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-99900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>129500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>15800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-17300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>43700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>26100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>13400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>22000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>13800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>1200</v>
       </c>
     </row>
